--- a/jogos_2026-01-08.xlsx
+++ b/jogos_2026-01-08.xlsx
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G21" t="n">

--- a/jogos_2026-01-08.xlsx
+++ b/jogos_2026-01-08.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1742,13 +1742,13 @@
         <v>5</v>
       </c>
       <c r="P11" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="R11" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="S11" t="n">
         <v>3.98</v>
@@ -1760,7 +1760,7 @@
         <v>1.75</v>
       </c>
       <c r="V11" t="n">
-        <v>3.95</v>
+        <v>3.94</v>
       </c>
       <c r="W11" t="n">
         <v>1.17</v>
@@ -1772,10 +1772,10 @@
         <v>1.06</v>
       </c>
       <c r="Z11" t="n">
-        <v>6.45</v>
+        <v>6.25</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AB11" t="n">
         <v>3</v>
@@ -1787,7 +1787,7 @@
         <v>1.93</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AF11" t="n">
         <v>2.5</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46030.60416666666</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46030.60416666666</v>
@@ -2215,28 +2215,28 @@
         <v>7.6</v>
       </c>
       <c r="O15" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="P15" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="Q15" t="n">
         <v>7</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S15" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="T15" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="U15" t="n">
         <v>1.37</v>
       </c>
       <c r="V15" t="n">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="W15" t="n">
         <v>1.06</v>
@@ -2245,10 +2245,10 @@
         <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.38</v>
+        <v>3.12</v>
       </c>
       <c r="AA15" t="n">
         <v>1.98</v>
@@ -2269,10 +2269,10 @@
         <v>1.61</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.87</v>
+        <v>2.69</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46030.69791666666</v>
@@ -2337,37 +2337,37 @@
         <v>2.15</v>
       </c>
       <c r="P16" t="n">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.67</v>
+        <v>5.1</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S16" t="n">
         <v>3.25</v>
       </c>
       <c r="T16" t="n">
-        <v>2.45</v>
+        <v>2.57</v>
       </c>
       <c r="U16" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="V16" t="n">
         <v>6</v>
       </c>
       <c r="W16" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X16" t="n">
         <v>1</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="AA16" t="n">
         <v>1.75</v>
@@ -2376,7 +2376,7 @@
         <v>2.1</v>
       </c>
       <c r="AC16" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="AD16" t="n">
         <v>1.39</v>
@@ -2385,13 +2385,13 @@
         <v>1.8</v>
       </c>
       <c r="AF16" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46030.70833333334</v>
@@ -2468,7 +2468,7 @@
         <v>2.62</v>
       </c>
       <c r="T17" t="n">
-        <v>2.55</v>
+        <v>2.9</v>
       </c>
       <c r="U17" t="n">
         <v>1.35</v>
@@ -2501,13 +2501,13 @@
         <v>1.24</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH17" t="n">
         <v>1.68</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G21" t="n">

--- a/jogos_2026-01-08.xlsx
+++ b/jogos_2026-01-08.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G21" t="n">

--- a/jogos_2026-01-08.xlsx
+++ b/jogos_2026-01-08.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46030.60416666666</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46030.60416666666</v>
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="M17" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="N17" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="O17" t="n">
         <v>2.5</v>
@@ -2471,7 +2471,7 @@
         <v>2.9</v>
       </c>
       <c r="U17" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="V17" t="n">
         <v>7.3</v>
@@ -2486,19 +2486,19 @@
         <v>1.32</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AC17" t="n">
         <v>3.25</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AE17" t="n">
         <v>1.85</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G21" t="n">

--- a/jogos_2026-01-08.xlsx
+++ b/jogos_2026-01-08.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1424,10 +1424,10 @@
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1754,7 +1754,7 @@
         <v>3.98</v>
       </c>
       <c r="T11" t="n">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="U11" t="n">
         <v>1.75</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46030.60416666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46030.60416666666</v>
@@ -2233,13 +2233,13 @@
         <v>2.8</v>
       </c>
       <c r="U15" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="V15" t="n">
         <v>7.3</v>
       </c>
       <c r="W15" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X15" t="n">
         <v>1.01</v>
@@ -2272,7 +2272,7 @@
         <v>1.05</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46030.69791666666</v>
@@ -2340,10 +2340,10 @@
         <v>2.18</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="R16" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S16" t="n">
         <v>3.25</v>
@@ -2352,13 +2352,13 @@
         <v>2.57</v>
       </c>
       <c r="U16" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="V16" t="n">
         <v>6</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X16" t="n">
         <v>1</v>
@@ -2367,7 +2367,7 @@
         <v>1.21</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="AA16" t="n">
         <v>1.75</v>
@@ -2376,7 +2376,7 @@
         <v>2.1</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="AD16" t="n">
         <v>1.39</v>
@@ -2385,13 +2385,13 @@
         <v>1.8</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46030.70833333334</v>
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="M17" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="N17" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="O17" t="n">
         <v>2.5</v>
@@ -2489,10 +2489,10 @@
         <v>3.3</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AC17" t="n">
         <v>3.25</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G20" t="n">

--- a/jogos_2026-01-08.xlsx
+++ b/jogos_2026-01-08.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>7.25</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46030.60416666666</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.17</v>
+        <v>1.95</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46030.60416666666</v>
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="M16" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="N16" t="n">
-        <v>5.3</v>
+        <v>5.45</v>
       </c>
       <c r="O16" t="n">
         <v>2.15</v>
@@ -2340,10 +2340,10 @@
         <v>2.18</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="R16" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S16" t="n">
         <v>3.25</v>
@@ -2352,7 +2352,7 @@
         <v>2.57</v>
       </c>
       <c r="U16" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="V16" t="n">
         <v>6</v>
@@ -2361,19 +2361,19 @@
         <v>1.11</v>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AC16" t="n">
         <v>3</v>
@@ -2388,10 +2388,10 @@
         <v>2</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46030.70833333334</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G21" t="n">

--- a/jogos_2026-01-08.xlsx
+++ b/jogos_2026-01-08.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1174,10 +1174,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.21</v>
+        <v>1.54</v>
       </c>
       <c r="M12" t="n">
-        <v>3.17</v>
+        <v>4</v>
       </c>
       <c r="N12" t="n">
-        <v>3.31</v>
+        <v>4.55</v>
       </c>
       <c r="O12" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.17</v>
+        <v>1.44</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.7</v>
+        <v>2.62</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46030.60416666666</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.44</v>
+        <v>1.95</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.62</v>
+        <v>1.85</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.95</v>
+        <v>2.28</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46030.60416666666</v>
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="M15" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="N15" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="O15" t="n">
         <v>1.96</v>
@@ -2227,10 +2227,10 @@
         <v>1.42</v>
       </c>
       <c r="S15" t="n">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="T15" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="U15" t="n">
         <v>1.39</v>
@@ -2239,40 +2239,40 @@
         <v>7.3</v>
       </c>
       <c r="W15" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X15" t="n">
         <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.12</v>
+        <v>3.35</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.98</v>
+        <v>2.03</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="AC15" t="n">
         <v>3.55</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.05</v>
+        <v>1.23</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.71</v>
+        <v>2.88</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46030.69791666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G21" t="n">

--- a/jogos_2026-01-08.xlsx
+++ b/jogos_2026-01-08.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1055,10 +1055,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1174,10 +1174,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.44</v>
+        <v>1.95</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.62</v>
+        <v>1.85</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.95</v>
+        <v>1.44</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.85</v>
+        <v>2.62</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2456,7 +2456,7 @@
         <v>2.5</v>
       </c>
       <c r="P17" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="Q17" t="n">
         <v>3.65</v>
@@ -2468,25 +2468,25 @@
         <v>2.62</v>
       </c>
       <c r="T17" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="U17" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="V17" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="W17" t="n">
         <v>1.03</v>
       </c>
       <c r="X17" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
         <v>1.32</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="AA17" t="n">
         <v>1.85</v>
@@ -2495,16 +2495,16 @@
         <v>1.85</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AG17" t="n">
         <v>1.3</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G21" t="n">

--- a/jogos_2026-01-08.xlsx
+++ b/jogos_2026-01-08.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -936,10 +936,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1055,10 +1055,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.95</v>
+        <v>2.28</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46030.60416666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.28</v>
+        <v>1.95</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46030.60416666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G21" t="n">

--- a/jogos_2026-01-08.xlsx
+++ b/jogos_2026-01-08.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -936,10 +936,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1174,10 +1174,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1382,46 +1382,46 @@
         <v>1.3</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>6.34</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AC8" t="n">
         <v>2.02</v>
@@ -1430,16 +1430,16 @@
         <v>1.7</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46030.47916666666</v>
@@ -1748,13 +1748,13 @@
         <v>1.81</v>
       </c>
       <c r="R11" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="S11" t="n">
         <v>3.98</v>
       </c>
       <c r="T11" t="n">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="U11" t="n">
         <v>1.75</v>
@@ -1772,7 +1772,7 @@
         <v>1.06</v>
       </c>
       <c r="Z11" t="n">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="AA11" t="n">
         <v>1.33</v>
@@ -1793,10 +1793,10 @@
         <v>2.5</v>
       </c>
       <c r="AG11" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AH11" t="n">
         <v>1.11</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.06</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46030.5625</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.3</v>
+        <v>1.54</v>
       </c>
       <c r="M12" t="n">
-        <v>3.14</v>
+        <v>4</v>
       </c>
       <c r="N12" t="n">
-        <v>3.1</v>
+        <v>4.55</v>
       </c>
       <c r="O12" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.28</v>
+        <v>1.44</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.65</v>
+        <v>2.62</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46030.60416666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.54</v>
+        <v>2.21</v>
       </c>
       <c r="M13" t="n">
-        <v>4</v>
+        <v>3.17</v>
       </c>
       <c r="N13" t="n">
-        <v>4.55</v>
+        <v>3.31</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.44</v>
+        <v>2.17</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.62</v>
+        <v>1.7</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46030.60416666666</v>
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="M15" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="N15" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="O15" t="n">
         <v>1.96</v>
@@ -2236,10 +2236,10 @@
         <v>1.39</v>
       </c>
       <c r="V15" t="n">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X15" t="n">
         <v>1.01</v>
@@ -2251,16 +2251,16 @@
         <v>3.35</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.03</v>
+        <v>1.98</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="AC15" t="n">
         <v>3.55</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AE15" t="n">
         <v>2.23</v>
@@ -2325,55 +2325,55 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="M16" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="N16" t="n">
-        <v>5.45</v>
+        <v>5.3</v>
       </c>
       <c r="O16" t="n">
         <v>2.15</v>
       </c>
       <c r="P16" t="n">
-        <v>2.18</v>
+        <v>2.35</v>
       </c>
       <c r="Q16" t="n">
         <v>5.1</v>
       </c>
       <c r="R16" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S16" t="n">
-        <v>3.25</v>
+        <v>3.32</v>
       </c>
       <c r="T16" t="n">
         <v>2.57</v>
       </c>
       <c r="U16" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="V16" t="n">
         <v>6</v>
       </c>
       <c r="W16" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AC16" t="n">
         <v>3</v>
@@ -2382,16 +2382,16 @@
         <v>1.39</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AF16" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AG16" t="n">
         <v>1.25</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.22</v>
+        <v>2.33</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46030.70833333334</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G20" t="n">

--- a/jogos_2026-01-08.xlsx
+++ b/jogos_2026-01-08.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1055,10 +1055,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1174,10 +1174,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1418,7 +1418,7 @@
         <v>5.25</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AB8" t="n">
         <v>2.46</v>
@@ -1742,28 +1742,28 @@
         <v>5</v>
       </c>
       <c r="P11" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="Q11" t="n">
         <v>1.81</v>
       </c>
       <c r="R11" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="S11" t="n">
-        <v>3.98</v>
+        <v>4.05</v>
       </c>
       <c r="T11" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="U11" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="V11" t="n">
-        <v>3.94</v>
+        <v>3.88</v>
       </c>
       <c r="W11" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
@@ -1772,10 +1772,10 @@
         <v>1.06</v>
       </c>
       <c r="Z11" t="n">
-        <v>6.5</v>
+        <v>6.45</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AB11" t="n">
         <v>3</v>
@@ -1787,16 +1787,16 @@
         <v>1.93</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AF11" t="n">
         <v>2.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46030.5625</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.54</v>
+        <v>2.21</v>
       </c>
       <c r="M12" t="n">
-        <v>4</v>
+        <v>3.17</v>
       </c>
       <c r="N12" t="n">
-        <v>4.55</v>
+        <v>3.31</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.44</v>
+        <v>2.17</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.62</v>
+        <v>1.7</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46030.60416666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.17</v>
+        <v>1.95</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46030.60416666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.95</v>
+        <v>1.44</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.85</v>
+        <v>2.62</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2218,7 +2218,7 @@
         <v>1.96</v>
       </c>
       <c r="P15" t="n">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="Q15" t="n">
         <v>7</v>
@@ -2236,10 +2236,10 @@
         <v>1.39</v>
       </c>
       <c r="V15" t="n">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="W15" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X15" t="n">
         <v>1.01</v>
@@ -2364,10 +2364,10 @@
         <v>1</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AA16" t="n">
         <v>1.75</v>
@@ -2376,7 +2376,7 @@
         <v>2.1</v>
       </c>
       <c r="AC16" t="n">
-        <v>3</v>
+        <v>2.72</v>
       </c>
       <c r="AD16" t="n">
         <v>1.39</v>
@@ -2453,7 +2453,7 @@
         <v>3.6</v>
       </c>
       <c r="O17" t="n">
-        <v>2.5</v>
+        <v>2.73</v>
       </c>
       <c r="P17" t="n">
         <v>2</v>
@@ -2465,13 +2465,13 @@
         <v>1.42</v>
       </c>
       <c r="S17" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="T17" t="n">
-        <v>2.95</v>
+        <v>2.55</v>
       </c>
       <c r="U17" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="V17" t="n">
         <v>7.4</v>
@@ -2495,10 +2495,10 @@
         <v>1.85</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AE17" t="n">
         <v>1.79</v>
@@ -2510,7 +2510,7 @@
         <v>1.3</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46030.71875</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G21" t="n">

--- a/jogos_2026-01-08.xlsx
+++ b/jogos_2026-01-08.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -817,10 +817,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1055,10 +1055,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1213,12 +1213,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1323,7 +1323,7 @@
         <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
-        <v>46030.46527777778</v>
+        <v>46030.41666666666</v>
       </c>
     </row>
     <row r="8">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,76 +1373,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>6.34</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
-        <v>46030.47916666666</v>
+        <v>46030.41666666666</v>
       </c>
     </row>
     <row r="9">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>7.25</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1561,7 +1561,7 @@
         <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
-        <v>46030.49652777778</v>
+        <v>46030.46527777778</v>
       </c>
     </row>
     <row r="10">
@@ -1570,12 +1570,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,76 +1611,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>6.34</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AI10" s="3" t="n">
-        <v>46030.53125</v>
+        <v>46030.47916666666</v>
       </c>
     </row>
     <row r="11">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>5.4</v>
+        <v>1.09</v>
       </c>
       <c r="M11" t="n">
-        <v>5</v>
+        <v>7.25</v>
       </c>
       <c r="N11" t="n">
-        <v>1.38</v>
+        <v>13.5</v>
       </c>
       <c r="O11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
-        <v>46030.5625</v>
+        <v>46030.49652777778</v>
       </c>
     </row>
     <row r="12">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,76 +1849,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
-        <v>46030.60416666666</v>
+        <v>46030.53125</v>
       </c>
     </row>
     <row r="13">
@@ -1927,12 +1927,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,76 +1968,76 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.95</v>
+        <v>1.35</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.85</v>
+        <v>3</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AI13" s="3" t="n">
-        <v>46030.60416666666</v>
+        <v>46030.5625</v>
       </c>
     </row>
     <row r="14">
@@ -2046,12 +2046,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,76 +2087,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.54</v>
+        <v>1.77</v>
       </c>
       <c r="M14" t="n">
-        <v>4</v>
+        <v>3.15</v>
       </c>
       <c r="N14" t="n">
-        <v>4.55</v>
+        <v>4.6</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>5.78</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.44</v>
+        <v>2.49</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.62</v>
+        <v>1.42</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AI14" s="3" t="n">
-        <v>46030.60416666666</v>
+        <v>46030.57291666666</v>
       </c>
     </row>
     <row r="15">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,76 +2206,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
-        <v>46030.69791666666</v>
+        <v>46030.60416666666</v>
       </c>
     </row>
     <row r="16">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,76 +2325,76 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="M16" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="N16" t="n">
-        <v>5.3</v>
+        <v>4.55</v>
       </c>
       <c r="O16" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.1</v>
+        <v>2.62</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
-        <v>46030.70833333334</v>
+        <v>46030.60416666666</v>
       </c>
     </row>
     <row r="17">
@@ -2403,12 +2403,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,76 +2444,76 @@
         </is>
       </c>
       <c r="L17" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="O17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V17" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AF17" t="n">
         <v>1.85</v>
       </c>
-      <c r="M17" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="N17" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="O17" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V17" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.92</v>
-      </c>
       <c r="AG17" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AI17" s="3" t="n">
-        <v>46030.71875</v>
+        <v>46030.60416666666</v>
       </c>
     </row>
     <row r="18">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2632,7 +2632,7 @@
         <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
-        <v>46030.875</v>
+        <v>46030.66666666666</v>
       </c>
     </row>
     <row r="19">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,76 +2682,76 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AI19" s="3" t="n">
-        <v>46030.875</v>
+        <v>46030.69791666666</v>
       </c>
     </row>
     <row r="20">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,76 +2801,76 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AI20" s="3" t="n">
-        <v>46030.875</v>
+        <v>46030.70833333334</v>
       </c>
     </row>
     <row r="21">
@@ -2879,12 +2879,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,76 +2920,76 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI21" s="3" t="n">
-        <v>46030.875</v>
+        <v>46030.71875</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2026-01-08.xlsx
+++ b/jogos_2026-01-08.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -817,10 +817,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1293,10 +1293,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.95</v>
+        <v>2.17</v>
       </c>
       <c r="AB15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AF15" t="n">
         <v>1.85</v>
       </c>
-      <c r="AC15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>0</v>
-      </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46030.60416666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.17</v>
+        <v>1.95</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AC17" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46030.60416666666</v>

--- a/jogos_2026-01-08.xlsx
+++ b/jogos_2026-01-08.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -823,10 +823,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1293,10 +1293,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1412,10 +1412,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1635,31 +1635,31 @@
         <v>3.58</v>
       </c>
       <c r="T10" t="n">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
       <c r="U10" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="V10" t="n">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="W10" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="X10" t="n">
         <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z10" t="n">
         <v>5.25</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.46</v>
+        <v>2.55</v>
       </c>
       <c r="AC10" t="n">
         <v>2.02</v>
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1900,10 +1900,10 @@
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
@@ -1977,10 +1977,10 @@
         <v>1.38</v>
       </c>
       <c r="O13" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="P13" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="Q13" t="n">
         <v>1.81</v>
@@ -1989,19 +1989,19 @@
         <v>1.17</v>
       </c>
       <c r="S13" t="n">
-        <v>4.05</v>
+        <v>3.98</v>
       </c>
       <c r="T13" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="U13" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="V13" t="n">
-        <v>3.88</v>
+        <v>3.94</v>
       </c>
       <c r="W13" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X13" t="n">
         <v>1.01</v>
@@ -2010,10 +2010,10 @@
         <v>1.06</v>
       </c>
       <c r="Z13" t="n">
-        <v>6.45</v>
+        <v>6.25</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AB13" t="n">
         <v>3</v>
@@ -2025,10 +2025,10 @@
         <v>1.93</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AG13" t="n">
         <v>1.11</v>
@@ -2087,28 +2087,28 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="M14" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="N14" t="n">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="O14" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="P14" t="n">
         <v>2.02</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.78</v>
+        <v>5.73</v>
       </c>
       <c r="R14" t="n">
         <v>1.47</v>
       </c>
       <c r="S14" t="n">
-        <v>2.33</v>
+        <v>2.28</v>
       </c>
       <c r="T14" t="n">
         <v>3.58</v>
@@ -2123,25 +2123,25 @@
         <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="AA14" t="n">
         <v>2.49</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="AC14" t="n">
         <v>4.95</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AE14" t="n">
         <v>2.25</v>
@@ -2215,13 +2215,13 @@
         <v>3.31</v>
       </c>
       <c r="O15" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P15" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.55</v>
+        <v>3.86</v>
       </c>
       <c r="R15" t="n">
         <v>1.51</v>
@@ -2233,22 +2233,22 @@
         <v>3.1</v>
       </c>
       <c r="U15" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V15" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="W15" t="n">
         <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="Z15" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="AA15" t="n">
         <v>2.17</v>
@@ -2257,7 +2257,7 @@
         <v>1.7</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.3</v>
+        <v>4.05</v>
       </c>
       <c r="AD15" t="n">
         <v>1.2</v>
@@ -2269,10 +2269,10 @@
         <v>1.85</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46030.60416666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.44</v>
+        <v>1.95</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.62</v>
+        <v>1.85</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.95</v>
+        <v>1.44</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.85</v>
+        <v>2.62</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="M18" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="N18" t="n">
-        <v>4.95</v>
+        <v>4.75</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>6.22</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46030.66666666666</v>
@@ -2697,7 +2697,7 @@
         <v>2.28</v>
       </c>
       <c r="Q19" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="R19" t="n">
         <v>1.42</v>
@@ -2706,19 +2706,19 @@
         <v>2.83</v>
       </c>
       <c r="T19" t="n">
-        <v>2.85</v>
+        <v>2.96</v>
       </c>
       <c r="U19" t="n">
         <v>1.39</v>
       </c>
       <c r="V19" t="n">
-        <v>7.3</v>
+        <v>7</v>
       </c>
       <c r="W19" t="n">
         <v>1.06</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y19" t="n">
         <v>1.31</v>
@@ -2733,13 +2733,13 @@
         <v>1.77</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.55</v>
+        <v>3.61</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.23</v>
+        <v>2.36</v>
       </c>
       <c r="AF19" t="n">
         <v>1.6</v>
@@ -2813,37 +2813,37 @@
         <v>2.15</v>
       </c>
       <c r="P20" t="n">
-        <v>2.35</v>
+        <v>2.18</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="R20" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="S20" t="n">
         <v>3.32</v>
       </c>
       <c r="T20" t="n">
-        <v>2.57</v>
+        <v>2.66</v>
       </c>
       <c r="U20" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="V20" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="W20" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X20" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AA20" t="n">
         <v>1.75</v>
@@ -2852,16 +2852,16 @@
         <v>2.1</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AE20" t="n">
         <v>1.74</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.03</v>
+        <v>1.98</v>
       </c>
       <c r="AG20" t="n">
         <v>1.25</v>
@@ -2935,19 +2935,19 @@
         <v>2</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.65</v>
+        <v>4.3</v>
       </c>
       <c r="R21" t="n">
         <v>1.42</v>
       </c>
       <c r="S21" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="T21" t="n">
-        <v>2.55</v>
+        <v>2.95</v>
       </c>
       <c r="U21" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="V21" t="n">
         <v>7.4</v>
@@ -2956,10 +2956,10 @@
         <v>1.03</v>
       </c>
       <c r="X21" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="Z21" t="n">
         <v>3.05</v>

--- a/jogos_2026-01-08.xlsx
+++ b/jogos_2026-01-08.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1174,10 +1174,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1412,10 +1412,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1611,22 +1611,22 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>7</v>
+        <v>7.11</v>
       </c>
       <c r="M10" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="N10" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="O10" t="n">
-        <v>6.34</v>
+        <v>6.45</v>
       </c>
       <c r="P10" t="n">
-        <v>2.49</v>
+        <v>2.51</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="R10" t="n">
         <v>1.21</v>
@@ -1635,37 +1635,37 @@
         <v>3.58</v>
       </c>
       <c r="T10" t="n">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="U10" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="V10" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="W10" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="X10" t="n">
         <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.25</v>
+        <v>5.35</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.55</v>
+        <v>2.49</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AE10" t="n">
         <v>1.64</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>5.4</v>
+        <v>6.42</v>
       </c>
       <c r="M13" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="N13" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="O13" t="n">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="P13" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="R13" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S13" t="n">
-        <v>3.98</v>
+        <v>4</v>
       </c>
       <c r="T13" t="n">
         <v>1.95</v>
@@ -1998,10 +1998,10 @@
         <v>1.75</v>
       </c>
       <c r="V13" t="n">
-        <v>3.94</v>
+        <v>3.92</v>
       </c>
       <c r="W13" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X13" t="n">
         <v>1.01</v>
@@ -2010,7 +2010,7 @@
         <v>1.06</v>
       </c>
       <c r="Z13" t="n">
-        <v>6.25</v>
+        <v>6.38</v>
       </c>
       <c r="AA13" t="n">
         <v>1.33</v>
@@ -2019,16 +2019,16 @@
         <v>3</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.77</v>
+        <v>1.9</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AG13" t="n">
         <v>1.11</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.21</v>
+        <v>1.54</v>
       </c>
       <c r="M15" t="n">
-        <v>3.17</v>
+        <v>4</v>
       </c>
       <c r="N15" t="n">
-        <v>3.31</v>
+        <v>4.55</v>
       </c>
       <c r="O15" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.17</v>
+        <v>1.44</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.7</v>
+        <v>2.62</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46030.60416666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.54</v>
+        <v>2.3</v>
       </c>
       <c r="M17" t="n">
-        <v>4</v>
+        <v>3.11</v>
       </c>
       <c r="N17" t="n">
-        <v>4.55</v>
+        <v>3.1</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.44</v>
+        <v>2.25</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.62</v>
+        <v>1.7</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46030.60416666666</v>
@@ -2682,25 +2682,25 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="M19" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="N19" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="O19" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="P19" t="n">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="Q19" t="n">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
       <c r="R19" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S19" t="n">
         <v>2.83</v>
@@ -2718,37 +2718,37 @@
         <v>1.06</v>
       </c>
       <c r="X19" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
         <v>1.31</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.35</v>
+        <v>3.12</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="AC19" t="n">
         <v>3.61</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.36</v>
+        <v>2.23</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.88</v>
+        <v>2.71</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46030.69791666666</v>

--- a/jogos_2026-01-08.xlsx
+++ b/jogos_2026-01-08.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -823,10 +823,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.87</v>
+        <v>1.55</v>
       </c>
       <c r="M4" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="N4" t="n">
-        <v>2.04</v>
+        <v>4.65</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="AB4" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.8</v>
+        <v>2.87</v>
       </c>
       <c r="M6" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="N6" t="n">
-        <v>4.3</v>
+        <v>2.04</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1174,16 +1174,16 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1412,10 +1412,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="M14" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="N14" t="n">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
       <c r="O14" t="n">
         <v>2.51</v>
@@ -2102,7 +2102,7 @@
         <v>2.02</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.73</v>
+        <v>5</v>
       </c>
       <c r="R14" t="n">
         <v>1.47</v>
@@ -2126,16 +2126,16 @@
         <v>1.09</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.39</v>
+        <v>2.48</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="AC14" t="n">
         <v>4.95</v>
@@ -2150,10 +2150,10 @@
         <v>1.56</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.12</v>
+        <v>1.28</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46030.57291666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.44</v>
+        <v>1.95</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.62</v>
+        <v>1.85</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46030.60416666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.3</v>
+        <v>1.54</v>
       </c>
       <c r="M17" t="n">
-        <v>3.11</v>
+        <v>4</v>
       </c>
       <c r="N17" t="n">
-        <v>3.1</v>
+        <v>4.55</v>
       </c>
       <c r="O17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.25</v>
+        <v>1.44</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.7</v>
+        <v>2.62</v>
       </c>
       <c r="AC17" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46030.60416666666</v>
@@ -2563,22 +2563,22 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="M18" t="n">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="N18" t="n">
-        <v>4.75</v>
+        <v>4.95</v>
       </c>
       <c r="O18" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="P18" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.22</v>
+        <v>6.17</v>
       </c>
       <c r="R18" t="n">
         <v>1.56</v>
@@ -2602,10 +2602,10 @@
         <v>1.06</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="AA18" t="n">
         <v>2.52</v>
@@ -2614,16 +2614,16 @@
         <v>1.41</v>
       </c>
       <c r="AC18" t="n">
-        <v>5.05</v>
+        <v>5</v>
       </c>
       <c r="AD18" t="n">
         <v>1.1</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AG18" t="n">
         <v>1.27</v>
@@ -2920,70 +2920,70 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="M21" t="n">
-        <v>3.35</v>
+        <v>3.22</v>
       </c>
       <c r="N21" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="O21" t="n">
-        <v>2.73</v>
+        <v>2.51</v>
       </c>
       <c r="P21" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="Q21" t="n">
         <v>4.3</v>
       </c>
       <c r="R21" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="S21" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="T21" t="n">
-        <v>2.95</v>
+        <v>3.04</v>
       </c>
       <c r="U21" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="V21" t="n">
-        <v>7.4</v>
+        <v>7.9</v>
       </c>
       <c r="W21" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X21" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.05</v>
+        <v>2.84</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.85</v>
+        <v>2.12</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.42</v>
+        <v>3.72</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.79</v>
+        <v>1.98</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH21" t="n">
         <v>1.67</v>

--- a/jogos_2026-01-08.xlsx
+++ b/jogos_2026-01-08.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -817,10 +817,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="M8" t="n">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="N8" t="n">
-        <v>4.3</v>
+        <v>4.65</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1412,16 +1412,16 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.3</v>
+        <v>1.54</v>
       </c>
       <c r="M16" t="n">
-        <v>3.11</v>
+        <v>4</v>
       </c>
       <c r="N16" t="n">
-        <v>3.1</v>
+        <v>4.55</v>
       </c>
       <c r="O16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.25</v>
+        <v>1.44</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.7</v>
+        <v>2.62</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46030.60416666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.54</v>
+        <v>2.3</v>
       </c>
       <c r="M17" t="n">
-        <v>4</v>
+        <v>3.11</v>
       </c>
       <c r="N17" t="n">
-        <v>4.55</v>
+        <v>3.1</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.44</v>
+        <v>2.25</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.62</v>
+        <v>1.7</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46030.60416666666</v>
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="M21" t="n">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="N21" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="O21" t="n">
         <v>2.51</v>
@@ -2935,10 +2935,10 @@
         <v>2.07</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.3</v>
+        <v>4.35</v>
       </c>
       <c r="R21" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="S21" t="n">
         <v>2.56</v>
@@ -2959,16 +2959,16 @@
         <v>1.02</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="AA21" t="n">
         <v>2.12</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AC21" t="n">
         <v>3.72</v>
@@ -2986,7 +2986,7 @@
         <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46030.71875</v>

--- a/jogos_2026-01-08.xlsx
+++ b/jogos_2026-01-08.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.8</v>
+        <v>2.87</v>
       </c>
       <c r="M3" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="N3" t="n">
-        <v>4.3</v>
+        <v>2.04</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -817,16 +817,16 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -936,10 +936,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1293,10 +1293,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.55</v>
+        <v>3.29</v>
       </c>
       <c r="M8" t="n">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="N8" t="n">
-        <v>4.65</v>
+        <v>2.04</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1412,16 +1412,16 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="M14" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="N14" t="n">
-        <v>4.75</v>
+        <v>4.33</v>
       </c>
       <c r="O14" t="n">
         <v>2.51</v>
@@ -2105,7 +2105,7 @@
         <v>5</v>
       </c>
       <c r="R14" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="S14" t="n">
         <v>2.28</v>
@@ -2123,31 +2123,31 @@
         <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.48</v>
+        <v>2.39</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="AB14" t="n">
         <v>1.42</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.95</v>
+        <v>4.7</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AE14" t="n">
         <v>2.25</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="AG14" t="n">
         <v>1.28</v>
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="M17" t="n">
-        <v>3.11</v>
+        <v>3</v>
       </c>
       <c r="N17" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="O17" t="n">
         <v>3</v>
@@ -2459,40 +2459,40 @@
         <v>1.95</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="R17" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S17" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="T17" t="n">
         <v>3.2</v>
       </c>
       <c r="U17" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V17" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="W17" t="n">
         <v>1.04</v>
       </c>
       <c r="X17" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="Z17" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.25</v>
+        <v>2.39</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AC17" t="n">
         <v>4.3</v>
@@ -2501,16 +2501,16 @@
         <v>1.19</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46030.60416666666</v>
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="M18" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="N18" t="n">
-        <v>4.95</v>
+        <v>4.75</v>
       </c>
       <c r="O18" t="n">
         <v>2.43</v>
@@ -2578,7 +2578,7 @@
         <v>2</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.17</v>
+        <v>5.85</v>
       </c>
       <c r="R18" t="n">
         <v>1.56</v>
@@ -2602,10 +2602,10 @@
         <v>1.06</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="AA18" t="n">
         <v>2.52</v>
@@ -2614,7 +2614,7 @@
         <v>1.41</v>
       </c>
       <c r="AC18" t="n">
-        <v>5</v>
+        <v>5.05</v>
       </c>
       <c r="AD18" t="n">
         <v>1.1</v>
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="M19" t="n">
-        <v>4.2</v>
+        <v>4.48</v>
       </c>
       <c r="N19" t="n">
-        <v>7.8</v>
+        <v>8.33</v>
       </c>
       <c r="O19" t="n">
         <v>1.91</v>
@@ -2703,7 +2703,7 @@
         <v>1.4</v>
       </c>
       <c r="S19" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="T19" t="n">
         <v>2.96</v>
@@ -2721,7 +2721,7 @@
         <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z19" t="n">
         <v>3.12</v>
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="M20" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="N20" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="O20" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="P20" t="n">
-        <v>2.18</v>
+        <v>2.38</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.9</v>
+        <v>5.35</v>
       </c>
       <c r="R20" t="n">
         <v>1.32</v>
       </c>
       <c r="S20" t="n">
-        <v>3.32</v>
+        <v>3.18</v>
       </c>
       <c r="T20" t="n">
-        <v>2.66</v>
+        <v>2.53</v>
       </c>
       <c r="U20" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="V20" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="W20" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z20" t="n">
-        <v>4</v>
+        <v>3.86</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB20" t="n">
         <v>2.1</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.73</v>
+        <v>2.95</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46030.70833333334</v>
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.11</v>
+        <v>1.85</v>
       </c>
       <c r="M21" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="N21" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="O21" t="n">
         <v>2.51</v>
@@ -2965,10 +2965,10 @@
         <v>2.88</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.12</v>
+        <v>1.85</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AC21" t="n">
         <v>3.72</v>

--- a/jogos_2026-01-08.xlsx
+++ b/jogos_2026-01-08.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="M3" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="N3" t="n">
-        <v>2.04</v>
+        <v>2.6</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -817,16 +817,16 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.8</v>
+        <v>2.87</v>
       </c>
       <c r="M4" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="N4" t="n">
-        <v>4.3</v>
+        <v>2.04</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -936,16 +936,16 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.55</v>
+        <v>3.29</v>
       </c>
       <c r="M5" t="n">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="N5" t="n">
-        <v>4.65</v>
+        <v>2.04</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1055,16 +1055,16 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1293,10 +1293,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.29</v>
+        <v>1.8</v>
       </c>
       <c r="M8" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N8" t="n">
-        <v>2.04</v>
+        <v>4.3</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1412,10 +1412,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1611,22 +1611,22 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>7.11</v>
+        <v>7</v>
       </c>
       <c r="M10" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="N10" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="O10" t="n">
-        <v>6.45</v>
+        <v>6</v>
       </c>
       <c r="P10" t="n">
-        <v>2.51</v>
+        <v>2.72</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="R10" t="n">
         <v>1.21</v>
@@ -1656,16 +1656,16 @@
         <v>5.35</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.49</v>
+        <v>2.56</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.14</v>
+        <v>2.02</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AE10" t="n">
         <v>1.64</v>
@@ -1674,10 +1674,10 @@
         <v>2.1</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46030.47916666666</v>
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>6.42</v>
+        <v>5.4</v>
       </c>
       <c r="M13" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="N13" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="O13" t="n">
         <v>5.1</v>
@@ -1986,7 +1986,7 @@
         <v>1.8</v>
       </c>
       <c r="R13" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2007,7 +2007,7 @@
         <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="Z13" t="n">
         <v>6.38</v>
@@ -2016,13 +2016,13 @@
         <v>1.33</v>
       </c>
       <c r="AB13" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="AE13" t="n">
         <v>1.58</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.95</v>
+        <v>2.17</v>
       </c>
       <c r="AB15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AF15" t="n">
         <v>1.85</v>
       </c>
-      <c r="AC15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>0</v>
-      </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46030.60416666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
         <v>1.95</v>
       </c>
-      <c r="Q17" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V17" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2.39</v>
-      </c>
       <c r="AB17" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AC17" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46030.60416666666</v>
@@ -2685,10 +2685,10 @@
         <v>1.41</v>
       </c>
       <c r="M19" t="n">
-        <v>4.48</v>
+        <v>4.33</v>
       </c>
       <c r="N19" t="n">
-        <v>8.33</v>
+        <v>7.6</v>
       </c>
       <c r="O19" t="n">
         <v>1.91</v>
@@ -2727,10 +2727,10 @@
         <v>3.12</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="AC19" t="n">
         <v>3.61</v>
@@ -2801,28 +2801,28 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="M20" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="N20" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="O20" t="n">
-        <v>2.13</v>
+        <v>2.09</v>
       </c>
       <c r="P20" t="n">
         <v>2.38</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.35</v>
+        <v>5.1</v>
       </c>
       <c r="R20" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S20" t="n">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="T20" t="n">
         <v>2.53</v>
@@ -2834,10 +2834,10 @@
         <v>6</v>
       </c>
       <c r="W20" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X20" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y20" t="n">
         <v>1.22</v>
@@ -2846,7 +2846,7 @@
         <v>3.86</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB20" t="n">
         <v>2.1</v>
@@ -2855,19 +2855,19 @@
         <v>2.95</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.34</v>
+        <v>2.43</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46030.70833333334</v>

--- a/jogos_2026-01-08.xlsx
+++ b/jogos_2026-01-08.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="M3" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="N3" t="n">
-        <v>2.6</v>
+        <v>2.79</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46030.41666666666</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.87</v>
+        <v>1.55</v>
       </c>
       <c r="M4" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="N4" t="n">
-        <v>2.04</v>
+        <v>4.65</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="AB4" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.29</v>
+        <v>2.7</v>
       </c>
       <c r="M5" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="N5" t="n">
-        <v>2.04</v>
+        <v>2.6</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>4.76</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46030.41666666666</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="M6" t="n">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="N6" t="n">
-        <v>4.65</v>
+        <v>4.3</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1174,16 +1174,16 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.79</v>
+        <v>2.69</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.91</v>
+        <v>1.41</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.8</v>
+        <v>2.87</v>
       </c>
       <c r="M8" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="N8" t="n">
-        <v>4.3</v>
+        <v>2.04</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1412,16 +1412,16 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -2096,31 +2096,31 @@
         <v>4.33</v>
       </c>
       <c r="O14" t="n">
-        <v>2.51</v>
+        <v>2.49</v>
       </c>
       <c r="P14" t="n">
         <v>2.02</v>
       </c>
       <c r="Q14" t="n">
-        <v>5</v>
+        <v>6.01</v>
       </c>
       <c r="R14" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="S14" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="T14" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="U14" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="V14" t="n">
-        <v>9.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
         <v>1.06</v>
@@ -2132,28 +2132,28 @@
         <v>2.39</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.49</v>
+        <v>2.34</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="AC14" t="n">
         <v>4.7</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AG14" t="n">
         <v>1.28</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46030.57291666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
         <v>1.95</v>
       </c>
-      <c r="Q15" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V15" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.17</v>
-      </c>
       <c r="AB15" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46030.60416666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.54</v>
+        <v>2.21</v>
       </c>
       <c r="M16" t="n">
-        <v>4</v>
+        <v>3.17</v>
       </c>
       <c r="N16" t="n">
-        <v>4.55</v>
+        <v>3.31</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.44</v>
+        <v>2.17</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.62</v>
+        <v>1.7</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46030.60416666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.95</v>
+        <v>1.44</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.85</v>
+        <v>2.62</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2572,34 +2572,34 @@
         <v>4.75</v>
       </c>
       <c r="O18" t="n">
-        <v>2.43</v>
+        <v>2.33</v>
       </c>
       <c r="P18" t="n">
         <v>2</v>
       </c>
       <c r="Q18" t="n">
-        <v>5.85</v>
+        <v>6.66</v>
       </c>
       <c r="R18" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="S18" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="T18" t="n">
-        <v>3.58</v>
+        <v>3.34</v>
       </c>
       <c r="U18" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="V18" t="n">
-        <v>8.6</v>
+        <v>7.9</v>
       </c>
       <c r="W18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y18" t="n">
         <v>1.5</v>
@@ -2608,28 +2608,28 @@
         <v>2.4</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.52</v>
+        <v>2.32</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.41</v>
+        <v>1.54</v>
       </c>
       <c r="AC18" t="n">
-        <v>5.05</v>
+        <v>4.45</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46030.66666666666</v>
@@ -2703,7 +2703,7 @@
         <v>1.4</v>
       </c>
       <c r="S19" t="n">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="T19" t="n">
         <v>2.96</v>
@@ -2712,7 +2712,7 @@
         <v>1.39</v>
       </c>
       <c r="V19" t="n">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="W19" t="n">
         <v>1.06</v>
@@ -2721,7 +2721,7 @@
         <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z19" t="n">
         <v>3.12</v>
@@ -2742,7 +2742,7 @@
         <v>2.23</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AG19" t="n">
         <v>1.17</v>
@@ -2938,31 +2938,31 @@
         <v>4.35</v>
       </c>
       <c r="R21" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="S21" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="T21" t="n">
         <v>3.04</v>
       </c>
       <c r="U21" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="V21" t="n">
-        <v>7.9</v>
+        <v>8.1</v>
       </c>
       <c r="W21" t="n">
         <v>1.02</v>
       </c>
       <c r="X21" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="AA21" t="n">
         <v>1.85</v>
@@ -2971,22 +2971,22 @@
         <v>1.85</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.72</v>
+        <v>3.82</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AE21" t="n">
         <v>1.98</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46030.71875</v>

--- a/jogos_2026-01-08.xlsx
+++ b/jogos_2026-01-08.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.59</v>
+        <v>1.55</v>
       </c>
       <c r="M3" t="n">
-        <v>2.82</v>
+        <v>3.65</v>
       </c>
       <c r="N3" t="n">
-        <v>2.79</v>
+        <v>4.65</v>
       </c>
       <c r="O3" t="n">
-        <v>4.13</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>9.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.83</v>
+        <v>1.79</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.33</v>
+        <v>1.91</v>
       </c>
       <c r="AC3" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46030.41666666666</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.55</v>
+        <v>2.59</v>
       </c>
       <c r="M4" t="n">
-        <v>3.65</v>
+        <v>2.82</v>
       </c>
       <c r="N4" t="n">
-        <v>4.65</v>
+        <v>2.79</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.79</v>
+        <v>2.83</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.91</v>
+        <v>1.33</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46030.41666666666</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="M5" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="N5" t="n">
-        <v>2.6</v>
+        <v>2.04</v>
       </c>
       <c r="O5" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.76</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.59</v>
+        <v>1.72</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.39</v>
+        <v>2</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46030.41666666666</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="M6" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="N6" t="n">
-        <v>4.3</v>
+        <v>2.6</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>4.76</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.69</v>
+        <v>2.59</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46030.41666666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1293,16 +1293,16 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.95</v>
+        <v>2.17</v>
       </c>
       <c r="AB15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AF15" t="n">
         <v>1.85</v>
       </c>
-      <c r="AC15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>0</v>
-      </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46030.60416666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
         <v>1.95</v>
       </c>
-      <c r="Q16" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V16" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2.17</v>
-      </c>
       <c r="AB16" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46030.60416666666</v>

--- a/jogos_2026-01-08.xlsx
+++ b/jogos_2026-01-08.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="R3" t="n">
         <v>1.55</v>
       </c>
-      <c r="M3" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="N3" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.79</v>
+        <v>2.59</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.91</v>
+        <v>1.44</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46030.41666666666</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.59</v>
+        <v>3.65</v>
       </c>
       <c r="M4" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="N4" t="n">
-        <v>2.79</v>
+        <v>2.1</v>
       </c>
       <c r="O4" t="n">
-        <v>4.13</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
         <v>1.65</v>
       </c>
-      <c r="S4" t="n">
+      <c r="Z4" t="n">
         <v>2.1</v>
       </c>
-      <c r="T4" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="V4" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AA4" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46030.41666666666</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.87</v>
+        <v>1.55</v>
       </c>
       <c r="M5" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="N5" t="n">
-        <v>2.04</v>
+        <v>4.65</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="AB5" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46030.41666666666</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="M6" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="N6" t="n">
-        <v>2.6</v>
+        <v>4.3</v>
       </c>
       <c r="O6" t="n">
-        <v>2.9</v>
+        <v>2.58</v>
       </c>
       <c r="P6" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.76</v>
+        <v>5.6</v>
       </c>
       <c r="R6" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="S6" t="n">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="T6" t="n">
-        <v>3.76</v>
+        <v>3.58</v>
       </c>
       <c r="U6" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="V6" t="n">
-        <v>8.699999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="W6" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X6" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.59</v>
+        <v>2.69</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.9</v>
+        <v>5.05</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.19</v>
+        <v>2.27</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46030.41666666666</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.8</v>
+        <v>2.95</v>
       </c>
       <c r="M7" t="n">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="N7" t="n">
-        <v>4.3</v>
+        <v>2.2</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AG7" t="n">
         <v>1.53</v>
       </c>
-      <c r="Z7" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>0</v>
-      </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46030.41666666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46030.41666666666</v>
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46030.46527777778</v>
@@ -1620,40 +1620,40 @@
         <v>1.3</v>
       </c>
       <c r="O10" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="P10" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="Q10" t="n">
         <v>1.8</v>
       </c>
       <c r="R10" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S10" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="T10" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="U10" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="V10" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="W10" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X10" t="n">
         <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.35</v>
+        <v>5.1</v>
       </c>
       <c r="AA10" t="n">
         <v>1.45</v>
@@ -1668,16 +1668,16 @@
         <v>1.7</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46030.47916666666</v>
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="M12" t="n">
-        <v>4.7</v>
+        <v>4.75</v>
       </c>
       <c r="N12" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>6.34</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.33</v>
+        <v>2.04</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46030.53125</v>
@@ -1989,7 +1989,7 @@
         <v>1.17</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="T13" t="n">
         <v>1.95</v>
@@ -1998,19 +1998,19 @@
         <v>1.75</v>
       </c>
       <c r="V13" t="n">
-        <v>3.92</v>
+        <v>3.95</v>
       </c>
       <c r="W13" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X13" t="n">
         <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z13" t="n">
-        <v>6.38</v>
+        <v>6.32</v>
       </c>
       <c r="AA13" t="n">
         <v>1.33</v>
@@ -2096,19 +2096,19 @@
         <v>4.33</v>
       </c>
       <c r="O14" t="n">
-        <v>2.49</v>
+        <v>2.56</v>
       </c>
       <c r="P14" t="n">
         <v>2.02</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.01</v>
+        <v>5.85</v>
       </c>
       <c r="R14" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="S14" t="n">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="T14" t="n">
         <v>3.5</v>
@@ -2117,10 +2117,10 @@
         <v>1.22</v>
       </c>
       <c r="V14" t="n">
-        <v>8.300000000000001</v>
+        <v>10</v>
       </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X14" t="n">
         <v>1.06</v>
@@ -2144,16 +2144,16 @@
         <v>1.12</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.17</v>
+        <v>2.26</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46030.57291666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.21</v>
+        <v>1.54</v>
       </c>
       <c r="M15" t="n">
-        <v>3.17</v>
+        <v>4</v>
       </c>
       <c r="N15" t="n">
-        <v>3.31</v>
+        <v>4.55</v>
       </c>
       <c r="O15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.17</v>
+        <v>1.44</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.7</v>
+        <v>2.62</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46030.60416666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.95</v>
+        <v>2.17</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46030.60416666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.44</v>
+        <v>1.95</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.62</v>
+        <v>1.85</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2572,19 +2572,19 @@
         <v>4.75</v>
       </c>
       <c r="O18" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="P18" t="n">
         <v>2</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.66</v>
+        <v>6.32</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="S18" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="T18" t="n">
         <v>3.34</v>
@@ -2614,16 +2614,16 @@
         <v>1.54</v>
       </c>
       <c r="AC18" t="n">
-        <v>4.45</v>
+        <v>4.4</v>
       </c>
       <c r="AD18" t="n">
         <v>1.14</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG18" t="n">
         <v>1.26</v>
@@ -2703,19 +2703,19 @@
         <v>1.4</v>
       </c>
       <c r="S19" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="T19" t="n">
-        <v>2.96</v>
+        <v>2.93</v>
       </c>
       <c r="U19" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="V19" t="n">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="W19" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X19" t="n">
         <v>1.01</v>
@@ -2742,7 +2742,7 @@
         <v>2.23</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AG19" t="n">
         <v>1.17</v>
@@ -2816,7 +2816,7 @@
         <v>2.38</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="R20" t="n">
         <v>1.33</v>
@@ -2828,13 +2828,13 @@
         <v>2.53</v>
       </c>
       <c r="U20" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="V20" t="n">
         <v>6</v>
       </c>
       <c r="W20" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X20" t="n">
         <v>1.02</v>
@@ -2852,16 +2852,16 @@
         <v>2.1</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AE20" t="n">
         <v>1.77</v>
       </c>
       <c r="AF20" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG20" t="n">
         <v>1.11</v>
@@ -2932,10 +2932,10 @@
         <v>2.51</v>
       </c>
       <c r="P21" t="n">
-        <v>2.07</v>
+        <v>1.96</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.35</v>
+        <v>3.83</v>
       </c>
       <c r="R21" t="n">
         <v>1.46</v>
@@ -2962,7 +2962,7 @@
         <v>1.34</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="AA21" t="n">
         <v>1.85</v>
@@ -2974,19 +2974,19 @@
         <v>3.82</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.98</v>
+        <v>1.88</v>
       </c>
       <c r="AF21" t="n">
         <v>1.82</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46030.71875</v>

--- a/jogos_2026-01-08.xlsx
+++ b/jogos_2026-01-08.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="M5" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="N5" t="n">
-        <v>4.65</v>
+        <v>4.3</v>
       </c>
       <c r="O5" t="n">
-        <v>2.1</v>
+        <v>2.58</v>
       </c>
       <c r="P5" t="n">
-        <v>2.16</v>
+        <v>1.84</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="R5" t="n">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="S5" t="n">
-        <v>3.05</v>
+        <v>2.25</v>
       </c>
       <c r="T5" t="n">
-        <v>2.59</v>
+        <v>3.58</v>
       </c>
       <c r="U5" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="V5" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AB5" t="n">
         <v>1.41</v>
       </c>
-      <c r="V5" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.94</v>
-      </c>
       <c r="AC5" t="n">
-        <v>2.97</v>
+        <v>5.05</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.32</v>
+        <v>1.1</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.79</v>
+        <v>2.27</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.9</v>
+        <v>1.54</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46030.41666666666</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.8</v>
+        <v>2.95</v>
       </c>
       <c r="M6" t="n">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="N6" t="n">
-        <v>4.3</v>
+        <v>2.2</v>
       </c>
       <c r="O6" t="n">
-        <v>2.58</v>
+        <v>3.44</v>
       </c>
       <c r="P6" t="n">
-        <v>1.84</v>
+        <v>2.14</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.6</v>
+        <v>2.78</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="S6" t="n">
-        <v>2.25</v>
+        <v>2.96</v>
       </c>
       <c r="T6" t="n">
-        <v>3.58</v>
+        <v>2.56</v>
       </c>
       <c r="U6" t="n">
-        <v>1.21</v>
+        <v>1.42</v>
       </c>
       <c r="V6" t="n">
-        <v>8.9</v>
+        <v>6.15</v>
       </c>
       <c r="W6" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X6" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AG6" t="n">
         <v>1.53</v>
       </c>
-      <c r="Z6" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH6" t="n">
-        <v>1.75</v>
+        <v>1.38</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46030.41666666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.95</v>
+        <v>1.55</v>
       </c>
       <c r="M7" t="n">
-        <v>3.34</v>
+        <v>3.8</v>
       </c>
       <c r="N7" t="n">
-        <v>2.2</v>
+        <v>4.65</v>
       </c>
       <c r="O7" t="n">
-        <v>3.44</v>
+        <v>2.1</v>
       </c>
       <c r="P7" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.78</v>
+        <v>5.8</v>
       </c>
       <c r="R7" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="S7" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="T7" t="n">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="U7" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="V7" t="n">
-        <v>6.15</v>
+        <v>6.55</v>
       </c>
       <c r="W7" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X7" t="n">
         <v>1</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.7</v>
+        <v>3.68</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.78</v>
+        <v>2.97</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.66</v>
+        <v>1.79</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.18</v>
+        <v>1.9</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.53</v>
+        <v>1.18</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.38</v>
+        <v>2.2</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46030.41666666666</v>
@@ -1611,19 +1611,19 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="M10" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="N10" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="O10" t="n">
-        <v>6.4</v>
+        <v>6.67</v>
       </c>
       <c r="P10" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="Q10" t="n">
         <v>1.8</v>
@@ -1635,13 +1635,13 @@
         <v>3.5</v>
       </c>
       <c r="T10" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="U10" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="V10" t="n">
-        <v>4.9</v>
+        <v>4.95</v>
       </c>
       <c r="W10" t="n">
         <v>1.11</v>
@@ -1653,31 +1653,31 @@
         <v>1.17</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.1</v>
+        <v>5.02</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.56</v>
+        <v>2.38</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.02</v>
+        <v>2.25</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46030.47916666666</v>
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>5.4</v>
+        <v>5.75</v>
       </c>
       <c r="M13" t="n">
         <v>5</v>
       </c>
       <c r="N13" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="O13" t="n">
         <v>5.1</v>
@@ -2013,19 +2013,19 @@
         <v>6.32</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AB13" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="AF13" t="n">
         <v>2.5</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
         <v>1.95</v>
       </c>
-      <c r="Q16" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3.39</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V16" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2.17</v>
-      </c>
       <c r="AB16" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46030.60416666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.95</v>
+        <v>2.39</v>
       </c>
       <c r="AB17" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AF17" t="n">
         <v>1.85</v>
       </c>
-      <c r="AC17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>0</v>
-      </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46030.60416666666</v>
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="M19" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="N19" t="n">
-        <v>7.6</v>
+        <v>8.31</v>
       </c>
       <c r="O19" t="n">
         <v>1.91</v>
@@ -2727,10 +2727,10 @@
         <v>3.12</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.98</v>
+        <v>2.09</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="AC19" t="n">
         <v>3.61</v>

--- a/jogos_2026-01-08.xlsx
+++ b/jogos_2026-01-08.xlsx
@@ -668,64 +668,64 @@
         <v>2.05</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>4.86</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46030.29166666666</v>
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.7</v>
+        <v>2.95</v>
       </c>
       <c r="M3" t="n">
-        <v>2.9</v>
+        <v>3.34</v>
       </c>
       <c r="N3" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="O3" t="n">
-        <v>2.8</v>
+        <v>3.44</v>
       </c>
       <c r="P3" t="n">
-        <v>1.82</v>
+        <v>2.14</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.03</v>
+        <v>2.78</v>
       </c>
       <c r="R3" t="n">
-        <v>1.55</v>
+        <v>1.32</v>
       </c>
       <c r="S3" t="n">
-        <v>2.29</v>
+        <v>2.96</v>
       </c>
       <c r="T3" t="n">
-        <v>3.4</v>
+        <v>2.56</v>
       </c>
       <c r="U3" t="n">
-        <v>1.19</v>
+        <v>1.42</v>
       </c>
       <c r="V3" t="n">
-        <v>10</v>
+        <v>6.15</v>
       </c>
       <c r="W3" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X3" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.55</v>
+        <v>1.2</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.3</v>
+        <v>3.7</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.59</v>
+        <v>1.75</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.44</v>
+        <v>2.05</v>
       </c>
       <c r="AC3" t="n">
-        <v>5.3</v>
+        <v>2.78</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.09</v>
+        <v>1.34</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.19</v>
+        <v>1.66</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.59</v>
+        <v>2.18</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.31</v>
+        <v>1.53</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.65</v>
+        <v>1.38</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46030.41666666666</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.65</v>
+        <v>2.7</v>
       </c>
       <c r="M4" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O4" t="n">
         <v>2.8</v>
       </c>
-      <c r="N4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>5.03</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y4" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AH4" t="n">
         <v>1.65</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46030.41666666666</v>
@@ -1025,19 +1025,19 @@
         <v>4.3</v>
       </c>
       <c r="O5" t="n">
-        <v>2.58</v>
+        <v>2.3</v>
       </c>
       <c r="P5" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="S5" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="T5" t="n">
         <v>3.58</v>
@@ -1046,7 +1046,7 @@
         <v>1.21</v>
       </c>
       <c r="V5" t="n">
-        <v>8.9</v>
+        <v>9.1</v>
       </c>
       <c r="W5" t="n">
         <v>1.03</v>
@@ -1067,22 +1067,22 @@
         <v>1.41</v>
       </c>
       <c r="AC5" t="n">
-        <v>5.05</v>
+        <v>5.1</v>
       </c>
       <c r="AD5" t="n">
         <v>1.1</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.27</v>
+        <v>2.34</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="AG5" t="n">
         <v>1.3</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46030.41666666666</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.95</v>
+        <v>3.65</v>
       </c>
       <c r="M6" t="n">
-        <v>3.34</v>
+        <v>2.8</v>
       </c>
       <c r="N6" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="O6" t="n">
-        <v>3.44</v>
+        <v>4.33</v>
       </c>
       <c r="P6" t="n">
-        <v>2.14</v>
+        <v>1.7</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.78</v>
+        <v>3.3</v>
       </c>
       <c r="R6" t="n">
-        <v>1.32</v>
+        <v>1.69</v>
       </c>
       <c r="S6" t="n">
-        <v>2.96</v>
+        <v>2.02</v>
       </c>
       <c r="T6" t="n">
-        <v>2.56</v>
+        <v>4.2</v>
       </c>
       <c r="U6" t="n">
-        <v>1.42</v>
+        <v>1.15</v>
       </c>
       <c r="V6" t="n">
-        <v>6.15</v>
+        <v>10.5</v>
       </c>
       <c r="W6" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.2</v>
+        <v>1.65</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.7</v>
+        <v>2.1</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.75</v>
+        <v>3.21</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.05</v>
+        <v>1.3</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.78</v>
+        <v>6.55</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.34</v>
+        <v>1.05</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.66</v>
+        <v>2.41</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.18</v>
+        <v>1.48</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.53</v>
+        <v>1.37</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46030.41666666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.54</v>
+        <v>2.52</v>
       </c>
       <c r="M15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N15" t="n">
-        <v>4.55</v>
+        <v>3.27</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.44</v>
+        <v>2.39</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.62</v>
+        <v>1.61</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46030.60416666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.52</v>
+        <v>1.54</v>
       </c>
       <c r="M17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N17" t="n">
-        <v>3.27</v>
+        <v>4.55</v>
       </c>
       <c r="O17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.39</v>
+        <v>1.44</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.61</v>
+        <v>2.62</v>
       </c>
       <c r="AC17" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46030.60416666666</v>
@@ -2804,70 +2804,70 @@
         <v>1.57</v>
       </c>
       <c r="M20" t="n">
-        <v>4.4</v>
+        <v>4.15</v>
       </c>
       <c r="N20" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="O20" t="n">
-        <v>2.09</v>
+        <v>2.19</v>
       </c>
       <c r="P20" t="n">
         <v>2.38</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="R20" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S20" t="n">
-        <v>3.25</v>
+        <v>3.19</v>
       </c>
       <c r="T20" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="U20" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="V20" t="n">
         <v>6</v>
       </c>
       <c r="W20" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X20" t="n">
         <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.86</v>
+        <v>3.76</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AD20" t="n">
         <v>1.41</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AG20" t="n">
         <v>1.11</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46030.70833333334</v>

--- a/jogos_2026-01-08.xlsx
+++ b/jogos_2026-01-08.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.95</v>
+        <v>1.8</v>
       </c>
       <c r="M3" t="n">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="N3" t="n">
-        <v>2.2</v>
+        <v>4.3</v>
       </c>
       <c r="O3" t="n">
-        <v>3.44</v>
+        <v>2.3</v>
       </c>
       <c r="P3" t="n">
-        <v>2.14</v>
+        <v>1.83</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.78</v>
+        <v>5.8</v>
       </c>
       <c r="R3" t="n">
-        <v>1.32</v>
+        <v>1.59</v>
       </c>
       <c r="S3" t="n">
-        <v>2.96</v>
+        <v>2.18</v>
       </c>
       <c r="T3" t="n">
-        <v>2.56</v>
+        <v>3.58</v>
       </c>
       <c r="U3" t="n">
-        <v>1.42</v>
+        <v>1.21</v>
       </c>
       <c r="V3" t="n">
-        <v>6.15</v>
+        <v>9.1</v>
       </c>
       <c r="W3" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.2</v>
+        <v>1.53</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.7</v>
+        <v>2.35</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.75</v>
+        <v>2.69</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.05</v>
+        <v>1.41</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.78</v>
+        <v>5.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.34</v>
+        <v>1.1</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.66</v>
+        <v>2.34</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.18</v>
+        <v>1.51</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.38</v>
+        <v>1.79</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46030.41666666666</v>
@@ -906,22 +906,22 @@
         <v>2.6</v>
       </c>
       <c r="O4" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="P4" t="n">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.03</v>
+        <v>4.92</v>
       </c>
       <c r="R4" t="n">
         <v>1.55</v>
       </c>
       <c r="S4" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="T4" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="U4" t="n">
         <v>1.19</v>
@@ -954,16 +954,16 @@
         <v>1.09</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.19</v>
+        <v>2.31</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46030.41666666666</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.8</v>
+        <v>2.95</v>
       </c>
       <c r="M5" t="n">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="N5" t="n">
-        <v>4.3</v>
+        <v>2.2</v>
       </c>
       <c r="O5" t="n">
-        <v>2.3</v>
+        <v>3.44</v>
       </c>
       <c r="P5" t="n">
-        <v>1.83</v>
+        <v>2.14</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.8</v>
+        <v>2.78</v>
       </c>
       <c r="R5" t="n">
-        <v>1.59</v>
+        <v>1.32</v>
       </c>
       <c r="S5" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V5" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AF5" t="n">
         <v>2.18</v>
       </c>
-      <c r="T5" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="V5" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y5" t="n">
+      <c r="AG5" t="n">
         <v>1.53</v>
       </c>
-      <c r="Z5" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH5" t="n">
-        <v>1.79</v>
+        <v>1.38</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46030.41666666666</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.55</v>
+        <v>2.59</v>
       </c>
       <c r="M7" t="n">
-        <v>3.8</v>
+        <v>2.82</v>
       </c>
       <c r="N7" t="n">
-        <v>4.65</v>
+        <v>2.79</v>
       </c>
       <c r="O7" t="n">
-        <v>2.1</v>
+        <v>4.23</v>
       </c>
       <c r="P7" t="n">
-        <v>2.16</v>
+        <v>1.75</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.8</v>
+        <v>3.36</v>
       </c>
       <c r="R7" t="n">
-        <v>1.34</v>
+        <v>1.66</v>
       </c>
       <c r="S7" t="n">
-        <v>3.05</v>
+        <v>2.08</v>
       </c>
       <c r="T7" t="n">
-        <v>2.59</v>
+        <v>3.98</v>
       </c>
       <c r="U7" t="n">
-        <v>1.41</v>
+        <v>1.17</v>
       </c>
       <c r="V7" t="n">
-        <v>6.55</v>
+        <v>13</v>
       </c>
       <c r="W7" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.28</v>
+        <v>1.62</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.68</v>
+        <v>2.15</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.77</v>
+        <v>2.89</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.94</v>
+        <v>1.36</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.97</v>
+        <v>6.25</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.32</v>
+        <v>1.07</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.79</v>
+        <v>2.39</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.9</v>
+        <v>1.56</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46030.41666666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N8" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T8" t="n">
         <v>2.59</v>
       </c>
-      <c r="M8" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="N8" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="O8" t="n">
-        <v>4.11</v>
-      </c>
-      <c r="P8" t="n">
+      <c r="U8" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V8" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AE8" t="n">
         <v>1.79</v>
       </c>
-      <c r="Q8" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="V8" t="n">
-        <v>13</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>2.49</v>
-      </c>
       <c r="AF8" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.35</v>
+        <v>1.18</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.28</v>
+        <v>2.2</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46030.41666666666</v>
@@ -1492,31 +1492,31 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.45</v>
+        <v>2.67</v>
       </c>
       <c r="M9" t="n">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="N9" t="n">
-        <v>2.55</v>
+        <v>2.59</v>
       </c>
       <c r="O9" t="n">
-        <v>3.22</v>
+        <v>3.16</v>
       </c>
       <c r="P9" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="R9" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="S9" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="T9" t="n">
-        <v>3.72</v>
+        <v>3.68</v>
       </c>
       <c r="U9" t="n">
         <v>1.2</v>
@@ -1525,40 +1525,40 @@
         <v>8.9</v>
       </c>
       <c r="W9" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X9" t="n">
         <v>1.07</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="AB9" t="n">
         <v>1.44</v>
       </c>
       <c r="AC9" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AE9" t="n">
         <v>2.16</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46030.46527777778</v>
@@ -2096,19 +2096,19 @@
         <v>4.33</v>
       </c>
       <c r="O14" t="n">
-        <v>2.56</v>
+        <v>2.48</v>
       </c>
       <c r="P14" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.85</v>
+        <v>4.9</v>
       </c>
       <c r="R14" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="S14" t="n">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="T14" t="n">
         <v>3.5</v>
@@ -2117,13 +2117,13 @@
         <v>1.22</v>
       </c>
       <c r="V14" t="n">
-        <v>10</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="Y14" t="n">
         <v>1.51</v>
@@ -2141,19 +2141,19 @@
         <v>4.7</v>
       </c>
       <c r="AD14" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AG14" t="n">
         <v>1.12</v>
       </c>
-      <c r="AE14" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AH14" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46030.57291666666</v>
@@ -2206,10 +2206,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.52</v>
+        <v>2.45</v>
       </c>
       <c r="M15" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N15" t="n">
         <v>3.27</v>
@@ -2218,16 +2218,16 @@
         <v>3</v>
       </c>
       <c r="P15" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.92</v>
+        <v>3.94</v>
       </c>
       <c r="R15" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="S15" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="T15" t="n">
         <v>3.34</v>
@@ -2242,34 +2242,34 @@
         <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.73</v>
+        <v>2.95</v>
       </c>
       <c r="AA15" t="n">
         <v>2.39</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AC15" t="n">
         <v>4.25</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AE15" t="n">
         <v>1.87</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AH15" t="n">
         <v>1.58</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.95</v>
+        <v>1.44</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.85</v>
+        <v>2.62</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.44</v>
+        <v>1.95</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.62</v>
+        <v>1.85</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2572,25 +2572,25 @@
         <v>4.75</v>
       </c>
       <c r="O18" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="P18" t="n">
         <v>2</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.32</v>
+        <v>6.7</v>
       </c>
       <c r="R18" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="S18" t="n">
         <v>2.31</v>
       </c>
       <c r="T18" t="n">
-        <v>3.34</v>
+        <v>3.38</v>
       </c>
       <c r="U18" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="V18" t="n">
         <v>7.9</v>
@@ -2620,13 +2620,13 @@
         <v>1.14</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AH18" t="n">
         <v>1.87</v>
@@ -2685,7 +2685,7 @@
         <v>1.43</v>
       </c>
       <c r="M19" t="n">
-        <v>4.5</v>
+        <v>4.47</v>
       </c>
       <c r="N19" t="n">
         <v>8.31</v>
@@ -2694,10 +2694,10 @@
         <v>1.91</v>
       </c>
       <c r="P19" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="Q19" t="n">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
       <c r="R19" t="n">
         <v>1.4</v>
@@ -2718,19 +2718,19 @@
         <v>1.05</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z19" t="n">
         <v>3.12</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.09</v>
+        <v>2.02</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AC19" t="n">
         <v>3.61</v>
@@ -2739,16 +2739,16 @@
         <v>1.26</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="AF19" t="n">
         <v>1.64</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.71</v>
+        <v>2.9</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46030.69791666666</v>
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="M20" t="n">
-        <v>4.15</v>
+        <v>4.33</v>
       </c>
       <c r="N20" t="n">
-        <v>5.5</v>
+        <v>5.55</v>
       </c>
       <c r="O20" t="n">
         <v>2.19</v>
@@ -2816,10 +2816,10 @@
         <v>2.38</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="R20" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S20" t="n">
         <v>3.19</v>
@@ -2849,7 +2849,7 @@
         <v>1.82</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AC20" t="n">
         <v>2.9</v>
@@ -2932,19 +2932,19 @@
         <v>2.51</v>
       </c>
       <c r="P21" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.83</v>
+        <v>4.4</v>
       </c>
       <c r="R21" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S21" t="n">
-        <v>2.5</v>
+        <v>2.61</v>
       </c>
       <c r="T21" t="n">
-        <v>3.04</v>
+        <v>3.16</v>
       </c>
       <c r="U21" t="n">
         <v>1.3</v>
@@ -2962,7 +2962,7 @@
         <v>1.34</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="AA21" t="n">
         <v>1.85</v>
@@ -2971,10 +2971,10 @@
         <v>1.85</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.82</v>
+        <v>3.95</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AE21" t="n">
         <v>1.88</v>
@@ -2983,10 +2983,10 @@
         <v>1.82</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46030.71875</v>

--- a/jogos_2026-01-08.xlsx
+++ b/jogos_2026-01-08.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.8</v>
+        <v>3.65</v>
       </c>
       <c r="M3" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="N3" t="n">
-        <v>4.3</v>
+        <v>2.1</v>
       </c>
       <c r="O3" t="n">
-        <v>2.3</v>
+        <v>4.33</v>
       </c>
       <c r="P3" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.8</v>
+        <v>3.3</v>
       </c>
       <c r="R3" t="n">
-        <v>1.59</v>
+        <v>1.69</v>
       </c>
       <c r="S3" t="n">
-        <v>2.18</v>
+        <v>2.02</v>
       </c>
       <c r="T3" t="n">
-        <v>3.58</v>
+        <v>4.2</v>
       </c>
       <c r="U3" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="V3" t="n">
-        <v>9.1</v>
+        <v>10.5</v>
       </c>
       <c r="W3" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X3" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.69</v>
+        <v>3.21</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="AC3" t="n">
-        <v>5.1</v>
+        <v>6.55</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.34</v>
+        <v>2.41</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.79</v>
+        <v>1.26</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46030.41666666666</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="M4" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="N4" t="n">
-        <v>2.6</v>
+        <v>4.3</v>
       </c>
       <c r="O4" t="n">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="P4" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.92</v>
+        <v>5.8</v>
       </c>
       <c r="R4" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="S4" t="n">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="T4" t="n">
-        <v>3.45</v>
+        <v>3.58</v>
       </c>
       <c r="U4" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="V4" t="n">
-        <v>10</v>
+        <v>9.1</v>
       </c>
       <c r="W4" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X4" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.59</v>
+        <v>2.69</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AC4" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.31</v>
+        <v>2.34</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.67</v>
+        <v>1.79</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46030.41666666666</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.95</v>
+        <v>2.59</v>
       </c>
       <c r="M5" t="n">
-        <v>3.34</v>
+        <v>2.82</v>
       </c>
       <c r="N5" t="n">
-        <v>2.2</v>
+        <v>2.79</v>
       </c>
       <c r="O5" t="n">
-        <v>3.44</v>
+        <v>4.23</v>
       </c>
       <c r="P5" t="n">
-        <v>2.14</v>
+        <v>1.75</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.78</v>
+        <v>3.36</v>
       </c>
       <c r="R5" t="n">
-        <v>1.32</v>
+        <v>1.66</v>
       </c>
       <c r="S5" t="n">
-        <v>2.96</v>
+        <v>2.08</v>
       </c>
       <c r="T5" t="n">
-        <v>2.56</v>
+        <v>3.98</v>
       </c>
       <c r="U5" t="n">
-        <v>1.42</v>
+        <v>1.17</v>
       </c>
       <c r="V5" t="n">
-        <v>6.15</v>
+        <v>13</v>
       </c>
       <c r="W5" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.2</v>
+        <v>1.62</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.7</v>
+        <v>2.15</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.75</v>
+        <v>2.89</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.05</v>
+        <v>1.36</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.78</v>
+        <v>6.25</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.34</v>
+        <v>1.07</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.66</v>
+        <v>2.39</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.18</v>
+        <v>1.56</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46030.41666666666</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.65</v>
+        <v>2.95</v>
       </c>
       <c r="M6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O6" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V6" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC6" t="n">
         <v>2.8</v>
       </c>
-      <c r="N6" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="O6" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="T6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="V6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>6.55</v>
-      </c>
       <c r="AD6" t="n">
-        <v>1.05</v>
+        <v>1.34</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.41</v>
+        <v>1.61</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.48</v>
+        <v>2.16</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46030.41666666666</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.59</v>
+        <v>1.62</v>
       </c>
       <c r="M7" t="n">
-        <v>2.82</v>
+        <v>3.5</v>
       </c>
       <c r="N7" t="n">
-        <v>2.79</v>
+        <v>5.6</v>
       </c>
       <c r="O7" t="n">
-        <v>4.23</v>
+        <v>2.07</v>
       </c>
       <c r="P7" t="n">
-        <v>1.75</v>
+        <v>2.22</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.36</v>
+        <v>5.45</v>
       </c>
       <c r="R7" t="n">
-        <v>1.66</v>
+        <v>1.31</v>
       </c>
       <c r="S7" t="n">
-        <v>2.08</v>
+        <v>3.02</v>
       </c>
       <c r="T7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V7" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z7" t="n">
         <v>3.98</v>
       </c>
-      <c r="U7" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="V7" t="n">
-        <v>13</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AA7" t="n">
-        <v>2.89</v>
+        <v>1.9</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.36</v>
+        <v>1.8</v>
       </c>
       <c r="AC7" t="n">
-        <v>6.25</v>
+        <v>2.76</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.07</v>
+        <v>1.38</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.39</v>
+        <v>1.73</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.56</v>
+        <v>1.98</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.3</v>
+        <v>2.24</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46030.41666666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="R8" t="n">
         <v>1.55</v>
       </c>
-      <c r="M8" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="N8" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="O8" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.34</v>
-      </c>
       <c r="S8" t="n">
-        <v>3.05</v>
+        <v>2.28</v>
       </c>
       <c r="T8" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="V8" t="n">
+        <v>10</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA8" t="n">
         <v>2.59</v>
       </c>
-      <c r="U8" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V8" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y8" t="n">
+      <c r="AB8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AG8" t="n">
         <v>1.28</v>
       </c>
-      <c r="Z8" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AH8" t="n">
-        <v>2.2</v>
+        <v>1.67</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46030.41666666666</v>
@@ -1849,67 +1849,67 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>6.8</v>
+        <v>8.5</v>
       </c>
       <c r="M12" t="n">
-        <v>4.75</v>
+        <v>4.9</v>
       </c>
       <c r="N12" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="O12" t="n">
         <v>6.34</v>
       </c>
       <c r="P12" t="n">
-        <v>2.49</v>
+        <v>2.53</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="R12" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="S12" t="n">
-        <v>3.34</v>
+        <v>3.48</v>
       </c>
       <c r="T12" t="n">
-        <v>2.21</v>
+        <v>2.17</v>
       </c>
       <c r="U12" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="V12" t="n">
-        <v>4.8</v>
+        <v>4.55</v>
       </c>
       <c r="W12" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X12" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z12" t="n">
         <v>5.4</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.41</v>
+        <v>1.55</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.54</v>
+        <v>2.29</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AF12" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AG12" t="n">
         <v>1.12</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.45</v>
+        <v>1.54</v>
       </c>
       <c r="M15" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="N15" t="n">
-        <v>3.27</v>
+        <v>4.55</v>
       </c>
       <c r="O15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.39</v>
+        <v>1.44</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.65</v>
+        <v>2.62</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46030.60416666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.54</v>
+        <v>2.21</v>
       </c>
       <c r="M16" t="n">
-        <v>4</v>
+        <v>3.17</v>
       </c>
       <c r="N16" t="n">
-        <v>4.55</v>
+        <v>3.31</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.44</v>
+        <v>2.17</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.62</v>
+        <v>1.7</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46030.60416666666</v>
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="M19" t="n">
-        <v>4.47</v>
+        <v>4.33</v>
       </c>
       <c r="N19" t="n">
-        <v>8.31</v>
+        <v>7.6</v>
       </c>
       <c r="O19" t="n">
         <v>1.91</v>
@@ -2727,10 +2727,10 @@
         <v>3.12</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AC19" t="n">
         <v>3.61</v>

--- a/jogos_2026-01-08.xlsx
+++ b/jogos_2026-01-08.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.65</v>
+        <v>2.95</v>
       </c>
       <c r="M3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O3" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V3" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC3" t="n">
         <v>2.8</v>
       </c>
-      <c r="N3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="O3" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="T3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="V3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>6.55</v>
-      </c>
       <c r="AD3" t="n">
-        <v>1.05</v>
+        <v>1.34</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.41</v>
+        <v>1.61</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.48</v>
+        <v>2.16</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.37</v>
+        <v>1.23</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46030.41666666666</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.8</v>
+        <v>3.65</v>
       </c>
       <c r="M4" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="N4" t="n">
-        <v>4.3</v>
+        <v>2.1</v>
       </c>
       <c r="O4" t="n">
-        <v>2.3</v>
+        <v>4.33</v>
       </c>
       <c r="P4" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.8</v>
+        <v>3.3</v>
       </c>
       <c r="R4" t="n">
-        <v>1.59</v>
+        <v>1.69</v>
       </c>
       <c r="S4" t="n">
-        <v>2.18</v>
+        <v>2.02</v>
       </c>
       <c r="T4" t="n">
-        <v>3.58</v>
+        <v>4.2</v>
       </c>
       <c r="U4" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="V4" t="n">
-        <v>9.1</v>
+        <v>10.5</v>
       </c>
       <c r="W4" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.69</v>
+        <v>3.21</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="AC4" t="n">
-        <v>5.1</v>
+        <v>6.55</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.34</v>
+        <v>2.41</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.79</v>
+        <v>1.26</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46030.41666666666</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="V5" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA5" t="n">
         <v>2.59</v>
       </c>
-      <c r="M5" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="N5" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="O5" t="n">
-        <v>4.23</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="T5" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="V5" t="n">
-        <v>13</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>2.89</v>
-      </c>
       <c r="AB5" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AC5" t="n">
-        <v>6.25</v>
+        <v>5.3</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.39</v>
+        <v>2.21</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.3</v>
+        <v>1.67</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46030.41666666666</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,34 +1135,34 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.95</v>
+        <v>1.62</v>
       </c>
       <c r="M6" t="n">
         <v>3.5</v>
       </c>
       <c r="N6" t="n">
-        <v>2.2</v>
+        <v>5.6</v>
       </c>
       <c r="O6" t="n">
-        <v>3.83</v>
+        <v>2.03</v>
       </c>
       <c r="P6" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.64</v>
+        <v>5.64</v>
       </c>
       <c r="R6" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S6" t="n">
-        <v>2.96</v>
+        <v>3.02</v>
       </c>
       <c r="T6" t="n">
-        <v>2.56</v>
+        <v>2.51</v>
       </c>
       <c r="U6" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="V6" t="n">
         <v>6.1</v>
@@ -1171,37 +1171,37 @@
         <v>1.06</v>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.68</v>
+        <v>1.9</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.16</v>
+        <v>1.97</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.35</v>
+        <v>2.24</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46030.41666666666</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="M7" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="N7" t="n">
-        <v>5.6</v>
+        <v>4.3</v>
       </c>
       <c r="O7" t="n">
-        <v>2.07</v>
+        <v>2.3</v>
       </c>
       <c r="P7" t="n">
-        <v>2.22</v>
+        <v>1.83</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.45</v>
+        <v>5.8</v>
       </c>
       <c r="R7" t="n">
-        <v>1.31</v>
+        <v>1.59</v>
       </c>
       <c r="S7" t="n">
-        <v>3.02</v>
+        <v>2.18</v>
       </c>
       <c r="T7" t="n">
-        <v>2.5</v>
+        <v>3.58</v>
       </c>
       <c r="U7" t="n">
-        <v>1.44</v>
+        <v>1.21</v>
       </c>
       <c r="V7" t="n">
-        <v>6.05</v>
+        <v>9.1</v>
       </c>
       <c r="W7" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X7" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.22</v>
+        <v>1.53</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.98</v>
+        <v>2.35</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.9</v>
+        <v>2.69</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.8</v>
+        <v>1.41</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.76</v>
+        <v>5.1</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.38</v>
+        <v>1.1</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.73</v>
+        <v>2.34</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.98</v>
+        <v>1.51</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.24</v>
+        <v>1.79</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46030.41666666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="M8" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="N8" t="n">
-        <v>2.6</v>
+        <v>2.79</v>
       </c>
       <c r="O8" t="n">
-        <v>2.75</v>
+        <v>4.28</v>
       </c>
       <c r="P8" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.92</v>
+        <v>3.34</v>
       </c>
       <c r="R8" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="S8" t="n">
-        <v>2.28</v>
+        <v>2.07</v>
       </c>
       <c r="T8" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="U8" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="V8" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="W8" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.59</v>
+        <v>2.89</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.3</v>
+        <v>6.25</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.67</v>
+        <v>1.3</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46030.41666666666</v>
@@ -1501,34 +1501,34 @@
         <v>2.59</v>
       </c>
       <c r="O9" t="n">
-        <v>3.16</v>
+        <v>3.04</v>
       </c>
       <c r="P9" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.75</v>
+        <v>3.84</v>
       </c>
       <c r="R9" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="S9" t="n">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="T9" t="n">
-        <v>3.68</v>
+        <v>3.58</v>
       </c>
       <c r="U9" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="V9" t="n">
-        <v>8.9</v>
+        <v>9.5</v>
       </c>
       <c r="W9" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X9" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y9" t="n">
         <v>1.5</v>
@@ -1543,22 +1543,22 @@
         <v>1.44</v>
       </c>
       <c r="AC9" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="AD9" t="n">
         <v>1.1</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.16</v>
+        <v>2.11</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AG9" t="n">
         <v>1.3</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46030.46527777778</v>
@@ -1611,22 +1611,22 @@
         </is>
       </c>
       <c r="L10" t="n">
+        <v>7</v>
+      </c>
+      <c r="M10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="O10" t="n">
         <v>6.5</v>
       </c>
-      <c r="M10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="N10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="O10" t="n">
-        <v>6.67</v>
-      </c>
       <c r="P10" t="n">
-        <v>2.72</v>
+        <v>2.47</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="R10" t="n">
         <v>1.22</v>
@@ -1635,10 +1635,10 @@
         <v>3.5</v>
       </c>
       <c r="T10" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="U10" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="V10" t="n">
         <v>4.95</v>
@@ -1650,34 +1650,34 @@
         <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.02</v>
+        <v>4.98</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46030.47916666666</v>
@@ -1858,13 +1858,13 @@
         <v>1.3</v>
       </c>
       <c r="O12" t="n">
-        <v>6.34</v>
+        <v>6.28</v>
       </c>
       <c r="P12" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="R12" t="n">
         <v>1.22</v>
@@ -1888,7 +1888,7 @@
         <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z12" t="n">
         <v>5.4</v>
@@ -1909,7 +1909,7 @@
         <v>1.68</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="AG12" t="n">
         <v>1.12</v>
@@ -1968,19 +1968,19 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>5.75</v>
+        <v>5.4</v>
       </c>
       <c r="M13" t="n">
         <v>5</v>
       </c>
       <c r="N13" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="O13" t="n">
         <v>5.1</v>
       </c>
       <c r="P13" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="Q13" t="n">
         <v>1.8</v>
@@ -1989,16 +1989,16 @@
         <v>1.17</v>
       </c>
       <c r="S13" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="V13" t="n">
         <v>3.98</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="V13" t="n">
-        <v>3.95</v>
       </c>
       <c r="W13" t="n">
         <v>1.17</v>
@@ -2007,28 +2007,28 @@
         <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z13" t="n">
-        <v>6.32</v>
+        <v>6.15</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AB13" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="AG13" t="n">
         <v>1.11</v>
@@ -2096,13 +2096,13 @@
         <v>4.33</v>
       </c>
       <c r="O14" t="n">
-        <v>2.48</v>
+        <v>2.53</v>
       </c>
       <c r="P14" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.9</v>
+        <v>5.84</v>
       </c>
       <c r="R14" t="n">
         <v>1.56</v>
@@ -2123,7 +2123,7 @@
         <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="Y14" t="n">
         <v>1.51</v>
@@ -2141,16 +2141,16 @@
         <v>4.7</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.12</v>
+        <v>1.28</v>
       </c>
       <c r="AH14" t="n">
         <v>1.83</v>
@@ -2334,13 +2334,13 @@
         <v>3.31</v>
       </c>
       <c r="O16" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="P16" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.94</v>
+        <v>3.98</v>
       </c>
       <c r="R16" t="n">
         <v>1.53</v>
@@ -2355,7 +2355,7 @@
         <v>1.32</v>
       </c>
       <c r="V16" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="W16" t="n">
         <v>1.04</v>
@@ -2376,13 +2376,13 @@
         <v>1.7</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.25</v>
+        <v>4.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AF16" t="n">
         <v>1.89</v>
@@ -2572,31 +2572,31 @@
         <v>4.75</v>
       </c>
       <c r="O18" t="n">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="P18" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.7</v>
+        <v>6.56</v>
       </c>
       <c r="R18" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="S18" t="n">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="T18" t="n">
-        <v>3.38</v>
+        <v>3.34</v>
       </c>
       <c r="U18" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="V18" t="n">
-        <v>7.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X18" t="n">
         <v>1.05</v>
@@ -2614,22 +2614,22 @@
         <v>1.54</v>
       </c>
       <c r="AC18" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="AF18" t="n">
         <v>1.55</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.87</v>
+        <v>2.05</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46030.66666666666</v>
@@ -2694,13 +2694,13 @@
         <v>1.91</v>
       </c>
       <c r="P19" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="Q19" t="n">
-        <v>7.2</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S19" t="n">
         <v>2.8</v>
@@ -2718,13 +2718,13 @@
         <v>1.05</v>
       </c>
       <c r="X19" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.12</v>
+        <v>3.16</v>
       </c>
       <c r="AA19" t="n">
         <v>1.98</v>
@@ -2733,22 +2733,22 @@
         <v>1.77</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.61</v>
+        <v>3.44</v>
       </c>
       <c r="AD19" t="n">
         <v>1.26</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AG19" t="n">
         <v>1.23</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46030.69791666666</v>
@@ -2801,16 +2801,16 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="M20" t="n">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="N20" t="n">
-        <v>5.55</v>
+        <v>5.3</v>
       </c>
       <c r="O20" t="n">
-        <v>2.19</v>
+        <v>2.16</v>
       </c>
       <c r="P20" t="n">
         <v>2.38</v>
@@ -2819,10 +2819,10 @@
         <v>5.4</v>
       </c>
       <c r="R20" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="S20" t="n">
-        <v>3.19</v>
+        <v>3.21</v>
       </c>
       <c r="T20" t="n">
         <v>2.56</v>
@@ -2837,34 +2837,34 @@
         <v>1.11</v>
       </c>
       <c r="X20" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z20" t="n">
         <v>3.76</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AB20" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.9</v>
+        <v>2.77</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AE20" t="n">
         <v>1.79</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AH20" t="n">
         <v>2.46</v>
@@ -2938,16 +2938,16 @@
         <v>4.4</v>
       </c>
       <c r="R21" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S21" t="n">
-        <v>2.61</v>
+        <v>2.5</v>
       </c>
       <c r="T21" t="n">
-        <v>3.16</v>
+        <v>3.1</v>
       </c>
       <c r="U21" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="V21" t="n">
         <v>8.1</v>
@@ -2971,7 +2971,7 @@
         <v>1.85</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.95</v>
+        <v>3.55</v>
       </c>
       <c r="AD21" t="n">
         <v>1.19</v>

--- a/jogos_2026-01-08.xlsx
+++ b/jogos_2026-01-08.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.95</v>
+        <v>2.59</v>
       </c>
       <c r="M3" t="n">
-        <v>3.5</v>
+        <v>2.82</v>
       </c>
       <c r="N3" t="n">
-        <v>2.2</v>
+        <v>2.79</v>
       </c>
       <c r="O3" t="n">
-        <v>3.83</v>
+        <v>4.28</v>
       </c>
       <c r="P3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="T3" t="n">
+        <v>4</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="V3" t="n">
+        <v>13</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z3" t="n">
         <v>2.15</v>
       </c>
-      <c r="Q3" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V3" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>3.7</v>
-      </c>
       <c r="AA3" t="n">
-        <v>1.68</v>
+        <v>2.89</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.05</v>
+        <v>1.36</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.8</v>
+        <v>6.25</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.34</v>
+        <v>1.08</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.61</v>
+        <v>2.38</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.16</v>
+        <v>1.56</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46030.41666666666</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.65</v>
+        <v>1.8</v>
       </c>
       <c r="M4" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="N4" t="n">
-        <v>2.1</v>
+        <v>4.3</v>
       </c>
       <c r="O4" t="n">
-        <v>4.33</v>
+        <v>2.3</v>
       </c>
       <c r="P4" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.3</v>
+        <v>5.8</v>
       </c>
       <c r="R4" t="n">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="S4" t="n">
-        <v>2.02</v>
+        <v>2.18</v>
       </c>
       <c r="T4" t="n">
-        <v>4.2</v>
+        <v>3.58</v>
       </c>
       <c r="U4" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="V4" t="n">
-        <v>10.5</v>
+        <v>9.1</v>
       </c>
       <c r="W4" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X4" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.21</v>
+        <v>2.69</v>
       </c>
       <c r="AB4" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AG4" t="n">
         <v>1.3</v>
       </c>
-      <c r="AC4" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.37</v>
-      </c>
       <c r="AH4" t="n">
-        <v>1.26</v>
+        <v>1.79</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46030.41666666666</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.62</v>
+        <v>3.65</v>
       </c>
       <c r="M6" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="N6" t="n">
-        <v>5.6</v>
+        <v>2.1</v>
       </c>
       <c r="O6" t="n">
-        <v>2.03</v>
+        <v>4.33</v>
       </c>
       <c r="P6" t="n">
-        <v>2.21</v>
+        <v>1.7</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.64</v>
+        <v>3.3</v>
       </c>
       <c r="R6" t="n">
-        <v>1.31</v>
+        <v>1.69</v>
       </c>
       <c r="S6" t="n">
-        <v>3.02</v>
+        <v>2.02</v>
       </c>
       <c r="T6" t="n">
-        <v>2.51</v>
+        <v>4.2</v>
       </c>
       <c r="U6" t="n">
-        <v>1.44</v>
+        <v>1.15</v>
       </c>
       <c r="V6" t="n">
-        <v>6.1</v>
+        <v>10.5</v>
       </c>
       <c r="W6" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.17</v>
+        <v>1.65</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.95</v>
+        <v>2.1</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.9</v>
+        <v>3.21</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.78</v>
+        <v>6.55</v>
       </c>
       <c r="AD6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AG6" t="n">
         <v>1.37</v>
       </c>
-      <c r="AE6" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AH6" t="n">
-        <v>2.24</v>
+        <v>1.26</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46030.41666666666</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N7" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>5.64</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V7" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB7" t="n">
         <v>1.8</v>
       </c>
-      <c r="M7" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="O7" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="V7" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.41</v>
-      </c>
       <c r="AC7" t="n">
-        <v>5.1</v>
+        <v>2.78</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.1</v>
+        <v>1.37</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.34</v>
+        <v>1.73</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.51</v>
+        <v>1.97</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.79</v>
+        <v>2.24</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46030.41666666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.59</v>
+        <v>2.95</v>
       </c>
       <c r="M8" t="n">
-        <v>2.82</v>
+        <v>3.5</v>
       </c>
       <c r="N8" t="n">
-        <v>2.79</v>
+        <v>2.2</v>
       </c>
       <c r="O8" t="n">
-        <v>4.28</v>
+        <v>3.83</v>
       </c>
       <c r="P8" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.34</v>
+        <v>2.64</v>
       </c>
       <c r="R8" t="n">
-        <v>1.67</v>
+        <v>1.32</v>
       </c>
       <c r="S8" t="n">
-        <v>2.07</v>
+        <v>2.96</v>
       </c>
       <c r="T8" t="n">
-        <v>4</v>
+        <v>2.56</v>
       </c>
       <c r="U8" t="n">
-        <v>1.17</v>
+        <v>1.42</v>
       </c>
       <c r="V8" t="n">
-        <v>13</v>
+        <v>6.1</v>
       </c>
       <c r="W8" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X8" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.62</v>
+        <v>1.22</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.15</v>
+        <v>3.7</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.89</v>
+        <v>1.68</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.36</v>
+        <v>2.05</v>
       </c>
       <c r="AC8" t="n">
-        <v>6.25</v>
+        <v>2.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.08</v>
+        <v>1.34</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.38</v>
+        <v>1.61</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.56</v>
+        <v>2.16</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46030.41666666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.54</v>
+        <v>2.21</v>
       </c>
       <c r="M15" t="n">
-        <v>4</v>
+        <v>3.17</v>
       </c>
       <c r="N15" t="n">
-        <v>4.55</v>
+        <v>3.31</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.44</v>
+        <v>2.17</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.62</v>
+        <v>1.7</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46030.60416666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.21</v>
+        <v>1.54</v>
       </c>
       <c r="M16" t="n">
-        <v>3.17</v>
+        <v>4</v>
       </c>
       <c r="N16" t="n">
-        <v>3.31</v>
+        <v>4.55</v>
       </c>
       <c r="O16" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.17</v>
+        <v>1.44</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.7</v>
+        <v>2.62</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46030.60416666666</v>

--- a/jogos_2026-01-08.xlsx
+++ b/jogos_2026-01-08.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="V3" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA3" t="n">
         <v>2.59</v>
       </c>
-      <c r="M3" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="N3" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="O3" t="n">
-        <v>4.28</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="R3" t="n">
+      <c r="AB3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH3" t="n">
         <v>1.67</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="T3" t="n">
-        <v>4</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="V3" t="n">
-        <v>13</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1.3</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46030.41666666666</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.8</v>
+        <v>2.59</v>
       </c>
       <c r="M4" t="n">
-        <v>3.1</v>
+        <v>2.82</v>
       </c>
       <c r="N4" t="n">
-        <v>4.3</v>
+        <v>2.79</v>
       </c>
       <c r="O4" t="n">
-        <v>2.3</v>
+        <v>4.28</v>
       </c>
       <c r="P4" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.8</v>
+        <v>3.34</v>
       </c>
       <c r="R4" t="n">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="S4" t="n">
-        <v>2.18</v>
+        <v>2.07</v>
       </c>
       <c r="T4" t="n">
-        <v>3.58</v>
+        <v>4</v>
       </c>
       <c r="U4" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="V4" t="n">
-        <v>9.1</v>
+        <v>13</v>
       </c>
       <c r="W4" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AD4" t="n">
         <v>1.08</v>
       </c>
-      <c r="Y4" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AE4" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="AG4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH4" t="n">
         <v>1.3</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.79</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46030.41666666666</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="M5" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="N5" t="n">
-        <v>2.6</v>
+        <v>4.3</v>
       </c>
       <c r="O5" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="P5" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.92</v>
+        <v>5.8</v>
       </c>
       <c r="R5" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="S5" t="n">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="T5" t="n">
-        <v>3.74</v>
+        <v>3.58</v>
       </c>
       <c r="U5" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="V5" t="n">
-        <v>8.699999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="W5" t="n">
         <v>1.03</v>
       </c>
       <c r="X5" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.59</v>
+        <v>2.69</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AC5" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.21</v>
+        <v>2.34</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.67</v>
+        <v>1.79</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46030.41666666666</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.65</v>
+        <v>1.62</v>
       </c>
       <c r="M6" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="N6" t="n">
-        <v>2.1</v>
+        <v>5.6</v>
       </c>
       <c r="O6" t="n">
-        <v>4.33</v>
+        <v>2.03</v>
       </c>
       <c r="P6" t="n">
-        <v>1.7</v>
+        <v>2.21</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.3</v>
+        <v>5.64</v>
       </c>
       <c r="R6" t="n">
-        <v>1.69</v>
+        <v>1.31</v>
       </c>
       <c r="S6" t="n">
-        <v>2.02</v>
+        <v>3.02</v>
       </c>
       <c r="T6" t="n">
-        <v>4.2</v>
+        <v>2.51</v>
       </c>
       <c r="U6" t="n">
-        <v>1.15</v>
+        <v>1.44</v>
       </c>
       <c r="V6" t="n">
-        <v>10.5</v>
+        <v>6.1</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X6" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.65</v>
+        <v>1.17</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.1</v>
+        <v>3.95</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.21</v>
+        <v>1.9</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="AC6" t="n">
-        <v>6.55</v>
+        <v>2.78</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.05</v>
+        <v>1.37</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.41</v>
+        <v>1.73</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.48</v>
+        <v>1.97</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.37</v>
+        <v>1.18</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.26</v>
+        <v>2.24</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46030.41666666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,34 +1254,34 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.62</v>
+        <v>2.95</v>
       </c>
       <c r="M7" t="n">
         <v>3.5</v>
       </c>
       <c r="N7" t="n">
-        <v>5.6</v>
+        <v>2.2</v>
       </c>
       <c r="O7" t="n">
-        <v>2.03</v>
+        <v>3.83</v>
       </c>
       <c r="P7" t="n">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.64</v>
+        <v>2.64</v>
       </c>
       <c r="R7" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S7" t="n">
-        <v>3.02</v>
+        <v>2.96</v>
       </c>
       <c r="T7" t="n">
-        <v>2.51</v>
+        <v>2.56</v>
       </c>
       <c r="U7" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="V7" t="n">
         <v>6.1</v>
@@ -1293,34 +1293,34 @@
         <v>1.04</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.9</v>
+        <v>1.68</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.97</v>
+        <v>2.16</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.24</v>
+        <v>1.28</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46030.41666666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.95</v>
+        <v>3.65</v>
       </c>
       <c r="M8" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="N8" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="O8" t="n">
-        <v>3.83</v>
+        <v>4.33</v>
       </c>
       <c r="P8" t="n">
-        <v>2.15</v>
+        <v>1.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.64</v>
+        <v>3.3</v>
       </c>
       <c r="R8" t="n">
-        <v>1.32</v>
+        <v>1.69</v>
       </c>
       <c r="S8" t="n">
-        <v>2.96</v>
+        <v>2.02</v>
       </c>
       <c r="T8" t="n">
-        <v>2.56</v>
+        <v>4.2</v>
       </c>
       <c r="U8" t="n">
-        <v>1.42</v>
+        <v>1.15</v>
       </c>
       <c r="V8" t="n">
-        <v>6.1</v>
+        <v>10.5</v>
       </c>
       <c r="W8" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.22</v>
+        <v>1.65</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.7</v>
+        <v>2.1</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.68</v>
+        <v>3.21</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.05</v>
+        <v>1.3</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.8</v>
+        <v>6.55</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.34</v>
+        <v>1.05</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.61</v>
+        <v>2.41</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.16</v>
+        <v>1.48</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.23</v>
+        <v>1.37</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46030.41666666666</v>
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="M10" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="N10" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="O10" t="n">
-        <v>6.5</v>
+        <v>6.35</v>
       </c>
       <c r="P10" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="R10" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="S10" t="n">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="T10" t="n">
-        <v>2.29</v>
+        <v>2.24</v>
       </c>
       <c r="U10" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="V10" t="n">
-        <v>4.95</v>
+        <v>5.05</v>
       </c>
       <c r="W10" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X10" t="n">
         <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.98</v>
+        <v>4.9</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.56</v>
+        <v>2.46</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.02</v>
+        <v>2.27</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="AG10" t="n">
         <v>1.12</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46030.47916666666</v>
@@ -1968,37 +1968,37 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="M13" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="N13" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="O13" t="n">
         <v>5.1</v>
       </c>
       <c r="P13" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="Q13" t="n">
         <v>1.8</v>
       </c>
       <c r="R13" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="S13" t="n">
-        <v>3.96</v>
+        <v>4</v>
       </c>
       <c r="T13" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="U13" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="V13" t="n">
-        <v>3.98</v>
+        <v>4</v>
       </c>
       <c r="W13" t="n">
         <v>1.17</v>
@@ -2007,22 +2007,22 @@
         <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z13" t="n">
-        <v>6.15</v>
+        <v>6.25</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AB13" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.77</v>
+        <v>1.9</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AE13" t="n">
         <v>1.47</v>
@@ -2031,10 +2031,10 @@
         <v>2.42</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46030.5625</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.44</v>
+        <v>1.95</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.62</v>
+        <v>1.85</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.95</v>
+        <v>1.44</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.85</v>
+        <v>2.62</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>

--- a/jogos_2026-01-08.xlsx
+++ b/jogos_2026-01-08.xlsx
@@ -645,87 +645,87 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="M2" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="N2" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="O2" t="n">
-        <v>4.86</v>
+        <v>5.89</v>
       </c>
       <c r="P2" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.08</v>
+        <v>2.58</v>
       </c>
       <c r="R2" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="S2" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="T2" t="n">
-        <v>4.1</v>
+        <v>3.74</v>
       </c>
       <c r="U2" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="V2" t="n">
-        <v>9.699999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="W2" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X2" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="AD2" t="n">
         <v>1.09</v>
       </c>
-      <c r="Y2" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AE2" t="n">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46030.29166666666</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="M3" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="N3" t="n">
-        <v>2.6</v>
+        <v>2.79</v>
       </c>
       <c r="O3" t="n">
-        <v>2.5</v>
+        <v>4.28</v>
       </c>
       <c r="P3" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.92</v>
+        <v>3.34</v>
       </c>
       <c r="R3" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="S3" t="n">
-        <v>2.28</v>
+        <v>2.07</v>
       </c>
       <c r="T3" t="n">
-        <v>3.74</v>
+        <v>4</v>
       </c>
       <c r="U3" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="V3" t="n">
-        <v>8.699999999999999</v>
+        <v>13</v>
       </c>
       <c r="W3" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X3" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.59</v>
+        <v>2.89</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AC3" t="n">
-        <v>5.3</v>
+        <v>6.25</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.21</v>
+        <v>2.38</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.67</v>
+        <v>1.3</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46030.41666666666</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.59</v>
+        <v>3</v>
       </c>
       <c r="M4" t="n">
-        <v>2.82</v>
+        <v>2.45</v>
       </c>
       <c r="N4" t="n">
-        <v>2.79</v>
+        <v>2.5</v>
       </c>
       <c r="O4" t="n">
-        <v>4.28</v>
+        <v>3.8</v>
       </c>
       <c r="P4" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.34</v>
+        <v>3.62</v>
       </c>
       <c r="R4" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="S4" t="n">
-        <v>2.07</v>
+        <v>2.01</v>
       </c>
       <c r="T4" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="U4" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="V4" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="W4" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.15</v>
+        <v>2.01</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.89</v>
+        <v>3.08</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AC4" t="n">
-        <v>6.25</v>
+        <v>6.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.56</v>
+        <v>1.46</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46030.41666666666</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.8</v>
+        <v>3.05</v>
       </c>
       <c r="M5" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N5" t="n">
-        <v>4.3</v>
+        <v>2.2</v>
       </c>
       <c r="O5" t="n">
-        <v>2.3</v>
+        <v>3.78</v>
       </c>
       <c r="P5" t="n">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.8</v>
+        <v>2.62</v>
       </c>
       <c r="R5" t="n">
-        <v>1.59</v>
+        <v>1.32</v>
       </c>
       <c r="S5" t="n">
-        <v>2.18</v>
+        <v>2.96</v>
       </c>
       <c r="T5" t="n">
-        <v>3.58</v>
+        <v>2.5</v>
       </c>
       <c r="U5" t="n">
-        <v>1.21</v>
+        <v>1.43</v>
       </c>
       <c r="V5" t="n">
-        <v>9.1</v>
+        <v>6.05</v>
       </c>
       <c r="W5" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="X5" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.53</v>
+        <v>1.2</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.35</v>
+        <v>3.72</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.69</v>
+        <v>1.77</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.41</v>
+        <v>1.98</v>
       </c>
       <c r="AC5" t="n">
-        <v>5.1</v>
+        <v>2.78</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.1</v>
+        <v>1.34</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.34</v>
+        <v>1.61</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.51</v>
+        <v>2.16</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.79</v>
+        <v>1.4</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46030.41666666666</v>
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="M6" t="n">
-        <v>3.5</v>
+        <v>3.87</v>
       </c>
       <c r="N6" t="n">
-        <v>5.6</v>
+        <v>4.4</v>
       </c>
       <c r="O6" t="n">
-        <v>2.03</v>
+        <v>2.16</v>
       </c>
       <c r="P6" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.64</v>
+        <v>5.05</v>
       </c>
       <c r="R6" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="S6" t="n">
         <v>3.02</v>
       </c>
       <c r="T6" t="n">
-        <v>2.51</v>
+        <v>2.53</v>
       </c>
       <c r="U6" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="V6" t="n">
-        <v>6.1</v>
+        <v>6.25</v>
       </c>
       <c r="W6" t="n">
         <v>1.06</v>
       </c>
       <c r="X6" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46030.41666666666</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.95</v>
+        <v>1.85</v>
       </c>
       <c r="M7" t="n">
-        <v>3.5</v>
+        <v>2.82</v>
       </c>
       <c r="N7" t="n">
-        <v>2.2</v>
+        <v>4.58</v>
       </c>
       <c r="O7" t="n">
-        <v>3.83</v>
+        <v>2.66</v>
       </c>
       <c r="P7" t="n">
-        <v>2.15</v>
+        <v>1.76</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.64</v>
+        <v>6</v>
       </c>
       <c r="R7" t="n">
-        <v>1.32</v>
+        <v>1.67</v>
       </c>
       <c r="S7" t="n">
-        <v>2.96</v>
+        <v>2.05</v>
       </c>
       <c r="T7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="V7" t="n">
+        <v>11</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AE7" t="n">
         <v>2.56</v>
       </c>
-      <c r="U7" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V7" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.61</v>
-      </c>
       <c r="AF7" t="n">
-        <v>2.16</v>
+        <v>1.43</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.28</v>
+        <v>1.73</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46030.41666666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.65</v>
+        <v>2.7</v>
       </c>
       <c r="M8" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="N8" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="O8" t="n">
-        <v>4.33</v>
+        <v>2.5</v>
       </c>
       <c r="P8" t="n">
-        <v>1.7</v>
+        <v>1.86</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.3</v>
+        <v>4.92</v>
       </c>
       <c r="R8" t="n">
-        <v>1.69</v>
+        <v>1.55</v>
       </c>
       <c r="S8" t="n">
-        <v>2.02</v>
+        <v>2.28</v>
       </c>
       <c r="T8" t="n">
-        <v>4.2</v>
+        <v>3.74</v>
       </c>
       <c r="U8" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="V8" t="n">
-        <v>10.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W8" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X8" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.21</v>
+        <v>2.59</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AC8" t="n">
-        <v>6.55</v>
+        <v>5.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.41</v>
+        <v>2.21</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.48</v>
+        <v>1.58</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.26</v>
+        <v>1.67</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46030.41666666666</v>
@@ -1501,34 +1501,34 @@
         <v>2.59</v>
       </c>
       <c r="O9" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="P9" t="n">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.84</v>
+        <v>4.2</v>
       </c>
       <c r="R9" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="S9" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="T9" t="n">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="U9" t="n">
         <v>1.21</v>
       </c>
       <c r="V9" t="n">
-        <v>9.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W9" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y9" t="n">
         <v>1.5</v>
@@ -1543,22 +1543,22 @@
         <v>1.44</v>
       </c>
       <c r="AC9" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AD9" t="n">
         <v>1.1</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AG9" t="n">
         <v>1.3</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46030.46527777778</v>
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="M10" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="N10" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="O10" t="n">
         <v>6.35</v>
@@ -1656,16 +1656,16 @@
         <v>4.9</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.27</v>
+        <v>2.02</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AE10" t="n">
         <v>1.71</v>
@@ -1858,40 +1858,40 @@
         <v>1.3</v>
       </c>
       <c r="O12" t="n">
-        <v>6.28</v>
+        <v>6.73</v>
       </c>
       <c r="P12" t="n">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="R12" t="n">
         <v>1.22</v>
       </c>
       <c r="S12" t="n">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="T12" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="U12" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="V12" t="n">
-        <v>4.55</v>
+        <v>4.45</v>
       </c>
       <c r="W12" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.4</v>
+        <v>4.95</v>
       </c>
       <c r="AA12" t="n">
         <v>1.55</v>
@@ -1906,16 +1906,16 @@
         <v>1.68</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46030.53125</v>
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="M13" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="N13" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="O13" t="n">
         <v>5.1</v>
@@ -2013,16 +2013,16 @@
         <v>6.25</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AB13" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AE13" t="n">
         <v>1.47</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.17</v>
+        <v>1.95</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46030.60416666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.95</v>
+        <v>1.44</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.85</v>
+        <v>2.62</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.54</v>
+        <v>2.21</v>
       </c>
       <c r="M17" t="n">
-        <v>4</v>
+        <v>3.17</v>
       </c>
       <c r="N17" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="O17" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V17" t="n">
+        <v>9</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC17" t="n">
         <v>4.55</v>
       </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>0</v>
-      </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46030.60416666666</v>
@@ -2691,40 +2691,40 @@
         <v>7.6</v>
       </c>
       <c r="O19" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="P19" t="n">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="Q19" t="n">
-        <v>8.210000000000001</v>
+        <v>7</v>
       </c>
       <c r="R19" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S19" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="T19" t="n">
-        <v>2.93</v>
+        <v>3.17</v>
       </c>
       <c r="U19" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="V19" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="W19" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.16</v>
+        <v>3.17</v>
       </c>
       <c r="AA19" t="n">
         <v>1.98</v>
@@ -2733,22 +2733,22 @@
         <v>1.77</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.44</v>
+        <v>3.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.96</v>
+        <v>2.84</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46030.69791666666</v>
@@ -2929,28 +2929,28 @@
         <v>3.6</v>
       </c>
       <c r="O21" t="n">
-        <v>2.51</v>
+        <v>2.61</v>
       </c>
       <c r="P21" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.4</v>
+        <v>4.57</v>
       </c>
       <c r="R21" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="S21" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="T21" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="U21" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="V21" t="n">
-        <v>8.1</v>
+        <v>8.5</v>
       </c>
       <c r="W21" t="n">
         <v>1.02</v>
@@ -2959,10 +2959,10 @@
         <v>1.03</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.78</v>
+        <v>3.05</v>
       </c>
       <c r="AA21" t="n">
         <v>1.85</v>
@@ -2974,19 +2974,19 @@
         <v>3.55</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46030.71875</v>

--- a/jogos_2026-01-08.xlsx
+++ b/jogos_2026-01-08.xlsx
@@ -752,99 +752,99 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.59</v>
+        <v>2.11</v>
       </c>
       <c r="M3" t="n">
-        <v>2.82</v>
+        <v>3.05</v>
       </c>
       <c r="N3" t="n">
-        <v>2.79</v>
+        <v>3.61</v>
       </c>
       <c r="O3" t="n">
-        <v>4.28</v>
+        <v>2.93</v>
       </c>
       <c r="P3" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.34</v>
+        <v>4.3</v>
       </c>
       <c r="R3" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="S3" t="n">
-        <v>2.07</v>
+        <v>2.17</v>
       </c>
       <c r="T3" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="U3" t="n">
         <v>1.17</v>
       </c>
       <c r="V3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="W3" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X3" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.89</v>
+        <v>2.74</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AC3" t="n">
-        <v>6.25</v>
+        <v>5.8</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.3</v>
+        <v>1.59</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46030.41666666666</v>
@@ -880,20 +880,20 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,16 +1109,16 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -1131,77 +1131,77 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.66</v>
+        <v>2.25</v>
       </c>
       <c r="M6" t="n">
-        <v>3.87</v>
+        <v>3.2</v>
       </c>
       <c r="N6" t="n">
-        <v>4.4</v>
+        <v>2.79</v>
       </c>
       <c r="O6" t="n">
-        <v>2.16</v>
+        <v>3.14</v>
       </c>
       <c r="P6" t="n">
-        <v>2.19</v>
+        <v>1.77</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.05</v>
+        <v>4.5</v>
       </c>
       <c r="R6" t="n">
-        <v>1.33</v>
+        <v>1.65</v>
       </c>
       <c r="S6" t="n">
-        <v>3.02</v>
+        <v>2.2</v>
       </c>
       <c r="T6" t="n">
-        <v>2.53</v>
+        <v>3.75</v>
       </c>
       <c r="U6" t="n">
-        <v>1.48</v>
+        <v>1.17</v>
       </c>
       <c r="V6" t="n">
-        <v>6.25</v>
+        <v>9.4</v>
       </c>
       <c r="W6" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.18</v>
+        <v>1.61</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.6</v>
+        <v>2.12</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.72</v>
+        <v>3.05</v>
       </c>
       <c r="AB6" t="n">
-        <v>2</v>
+        <v>1.38</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.74</v>
+        <v>6.1</v>
       </c>
       <c r="AD6" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AG6" t="n">
         <v>1.35</v>
       </c>
-      <c r="AE6" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH6" t="n">
-        <v>2.1</v>
+        <v>1.49</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46030.41666666666</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,99 +1228,99 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="M7" t="n">
-        <v>2.82</v>
+        <v>3.87</v>
       </c>
       <c r="N7" t="n">
-        <v>4.58</v>
+        <v>4.4</v>
       </c>
       <c r="O7" t="n">
-        <v>2.66</v>
+        <v>2.16</v>
       </c>
       <c r="P7" t="n">
-        <v>1.76</v>
+        <v>2.19</v>
       </c>
       <c r="Q7" t="n">
-        <v>6</v>
+        <v>5.05</v>
       </c>
       <c r="R7" t="n">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="S7" t="n">
-        <v>2.05</v>
+        <v>3.02</v>
       </c>
       <c r="T7" t="n">
-        <v>4.1</v>
+        <v>2.53</v>
       </c>
       <c r="U7" t="n">
-        <v>1.16</v>
+        <v>1.48</v>
       </c>
       <c r="V7" t="n">
-        <v>11</v>
+        <v>6.25</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X7" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.69</v>
+        <v>1.18</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.02</v>
+        <v>3.6</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.02</v>
+        <v>1.72</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.29</v>
+        <v>2</v>
       </c>
       <c r="AC7" t="n">
-        <v>6.25</v>
+        <v>2.74</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.06</v>
+        <v>1.35</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.56</v>
+        <v>1.72</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.43</v>
+        <v>1.98</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46030.41666666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1369,77 +1369,77 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.7</v>
+        <v>1.85</v>
       </c>
       <c r="M8" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="N8" t="n">
-        <v>2.6</v>
+        <v>4.58</v>
       </c>
       <c r="O8" t="n">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="P8" t="n">
-        <v>1.86</v>
+        <v>1.76</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.92</v>
+        <v>6</v>
       </c>
       <c r="R8" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="S8" t="n">
-        <v>2.28</v>
+        <v>2.05</v>
       </c>
       <c r="T8" t="n">
-        <v>3.74</v>
+        <v>4.1</v>
       </c>
       <c r="U8" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="V8" t="n">
-        <v>8.699999999999999</v>
+        <v>11</v>
       </c>
       <c r="W8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X8" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.55</v>
+        <v>1.69</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.59</v>
+        <v>3.02</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.3</v>
+        <v>6.25</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.21</v>
+        <v>2.56</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.58</v>
+        <v>1.43</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46030.41666666666</v>
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="M12" t="n">
-        <v>4.9</v>
+        <v>4.33</v>
       </c>
       <c r="N12" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="O12" t="n">
-        <v>6.73</v>
+        <v>6.23</v>
       </c>
       <c r="P12" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="R12" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S12" t="n">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="T12" t="n">
         <v>2.15</v>
       </c>
       <c r="U12" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="V12" t="n">
-        <v>4.45</v>
+        <v>4.6</v>
       </c>
       <c r="W12" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.95</v>
+        <v>4.8</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.05</v>
+        <v>2.21</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.68</v>
+        <v>1.59</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.1</v>
+        <v>2.72</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46030.53125</v>
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="M14" t="n">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="N14" t="n">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
       <c r="O14" t="n">
-        <v>2.53</v>
+        <v>2.65</v>
       </c>
       <c r="P14" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.84</v>
+        <v>5</v>
       </c>
       <c r="R14" t="n">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="S14" t="n">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="T14" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="U14" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="V14" t="n">
-        <v>8.300000000000001</v>
+        <v>13</v>
       </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X14" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.51</v>
+        <v>1.63</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.39</v>
+        <v>2.19</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.34</v>
+        <v>2.9</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.7</v>
+        <v>4.75</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46030.57291666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.95</v>
+        <v>1.44</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.85</v>
+        <v>2.62</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.44</v>
+        <v>1.95</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.62</v>
+        <v>1.85</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="M18" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="N18" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="O18" t="n">
-        <v>2.09</v>
+        <v>2.25</v>
       </c>
       <c r="P18" t="n">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.56</v>
+        <v>5.6</v>
       </c>
       <c r="R18" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="S18" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="T18" t="n">
-        <v>3.34</v>
+        <v>3.58</v>
       </c>
       <c r="U18" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="V18" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="W18" t="n">
         <v>1.04</v>
       </c>
       <c r="X18" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="Y18" t="n">
         <v>1.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.4</v>
+        <v>2.47</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.32</v>
+        <v>2.49</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AC18" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46030.66666666666</v>
@@ -2810,40 +2810,40 @@
         <v>5.3</v>
       </c>
       <c r="O20" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="P20" t="n">
-        <v>2.38</v>
+        <v>2.19</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="R20" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="S20" t="n">
-        <v>3.21</v>
+        <v>3.02</v>
       </c>
       <c r="T20" t="n">
-        <v>2.56</v>
+        <v>2.78</v>
       </c>
       <c r="U20" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="V20" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.76</v>
+        <v>3.5</v>
       </c>
       <c r="AA20" t="n">
         <v>1.75</v>
@@ -2852,22 +2852,22 @@
         <v>2.1</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.77</v>
+        <v>3.19</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="AG20" t="n">
         <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.46</v>
+        <v>2.41</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46030.70833333334</v>

--- a/jogos_2026-01-08.xlsx
+++ b/jogos_2026-01-08.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,99 +752,99 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="M3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O3" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V3" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X3" t="n">
         <v>1</v>
       </c>
-      <c r="J3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="M3" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="N3" t="n">
-        <v>3.61</v>
-      </c>
-      <c r="O3" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="R3" t="n">
+      <c r="Y3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AE3" t="n">
         <v>1.61</v>
       </c>
-      <c r="S3" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="T3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="V3" t="n">
-        <v>11</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AB3" t="n">
+      <c r="AF3" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH3" t="n">
         <v>1.4</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1.59</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46030.41666666666</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,99 +871,99 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="M4" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="N4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V4" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X4" t="n">
         <v>1</v>
       </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
-        <v>3</v>
-      </c>
-      <c r="M4" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="N4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O4" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="T4" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="V4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.12</v>
-      </c>
       <c r="Y4" t="n">
-        <v>1.7</v>
+        <v>1.18</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.01</v>
+        <v>3.6</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.08</v>
+        <v>1.72</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.28</v>
+        <v>2</v>
       </c>
       <c r="AC4" t="n">
-        <v>6.6</v>
+        <v>2.74</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.05</v>
+        <v>1.35</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.41</v>
+        <v>1.72</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.46</v>
+        <v>1.98</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.32</v>
+        <v>2.1</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46030.41666666666</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,25 +990,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I5" t="n">
         <v>1</v>
       </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="M5" t="n">
         <v>3.05</v>
       </c>
-      <c r="M5" t="n">
-        <v>3.2</v>
-      </c>
       <c r="N5" t="n">
-        <v>2.2</v>
+        <v>3.61</v>
       </c>
       <c r="O5" t="n">
-        <v>3.78</v>
+        <v>2.93</v>
       </c>
       <c r="P5" t="n">
-        <v>2.15</v>
+        <v>1.84</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.62</v>
+        <v>4.3</v>
       </c>
       <c r="R5" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="V5" t="n">
+        <v>11</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AG5" t="n">
         <v>1.32</v>
       </c>
-      <c r="S5" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="V5" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AH5" t="n">
-        <v>1.4</v>
+        <v>1.59</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46030.41666666666</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,16 +1109,16 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="M6" t="n">
-        <v>3.2</v>
+        <v>2.82</v>
       </c>
       <c r="N6" t="n">
-        <v>2.79</v>
+        <v>4.58</v>
       </c>
       <c r="O6" t="n">
-        <v>3.14</v>
+        <v>2.66</v>
       </c>
       <c r="P6" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="R6" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="S6" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="T6" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="U6" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="V6" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="W6" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.61</v>
+        <v>1.69</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.05</v>
+        <v>3.02</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AC6" t="n">
-        <v>6.1</v>
+        <v>6.25</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.32</v>
+        <v>2.56</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.49</v>
+        <v>1.73</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46030.41666666666</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,22 +1228,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.66</v>
+        <v>2.25</v>
       </c>
       <c r="M7" t="n">
-        <v>3.87</v>
+        <v>3.2</v>
       </c>
       <c r="N7" t="n">
-        <v>4.4</v>
+        <v>2.79</v>
       </c>
       <c r="O7" t="n">
-        <v>2.16</v>
+        <v>3.14</v>
       </c>
       <c r="P7" t="n">
-        <v>2.19</v>
+        <v>1.77</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.05</v>
+        <v>4.5</v>
       </c>
       <c r="R7" t="n">
-        <v>1.33</v>
+        <v>1.65</v>
       </c>
       <c r="S7" t="n">
-        <v>3.02</v>
+        <v>2.2</v>
       </c>
       <c r="T7" t="n">
-        <v>2.53</v>
+        <v>3.75</v>
       </c>
       <c r="U7" t="n">
-        <v>1.48</v>
+        <v>1.17</v>
       </c>
       <c r="V7" t="n">
-        <v>6.25</v>
+        <v>9.4</v>
       </c>
       <c r="W7" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.18</v>
+        <v>1.61</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.6</v>
+        <v>2.12</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.72</v>
+        <v>3.05</v>
       </c>
       <c r="AB7" t="n">
-        <v>2</v>
+        <v>1.38</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.74</v>
+        <v>6.1</v>
       </c>
       <c r="AD7" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AG7" t="n">
         <v>1.35</v>
       </c>
-      <c r="AE7" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH7" t="n">
-        <v>2.1</v>
+        <v>1.49</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46030.41666666666</v>
@@ -1347,22 +1347,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1373,37 +1373,37 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.85</v>
+        <v>3</v>
       </c>
       <c r="M8" t="n">
-        <v>2.82</v>
+        <v>2.45</v>
       </c>
       <c r="N8" t="n">
-        <v>4.58</v>
+        <v>2.5</v>
       </c>
       <c r="O8" t="n">
-        <v>2.66</v>
+        <v>3.8</v>
       </c>
       <c r="P8" t="n">
-        <v>1.76</v>
+        <v>1.69</v>
       </c>
       <c r="Q8" t="n">
-        <v>6</v>
+        <v>3.62</v>
       </c>
       <c r="R8" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="S8" t="n">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="T8" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="U8" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="V8" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="W8" t="n">
         <v>1.01</v>
@@ -1412,34 +1412,34 @@
         <v>1.12</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.02</v>
+        <v>3.08</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AC8" t="n">
-        <v>6.25</v>
+        <v>6.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.56</v>
+        <v>2.41</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.73</v>
+        <v>1.32</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46030.41666666666</v>
@@ -1475,20 +1475,20 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -1713,90 +1713,90 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="M11" t="n">
-        <v>7.25</v>
+        <v>8</v>
       </c>
       <c r="N11" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46030.49652777778</v>
@@ -1832,20 +1832,20 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L12" t="n">
@@ -1951,90 +1951,90 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="M13" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="N13" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="O13" t="n">
         <v>5.1</v>
       </c>
       <c r="P13" t="n">
-        <v>2.6</v>
+        <v>2.74</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="R13" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="T13" t="n">
-        <v>1.99</v>
+        <v>1.92</v>
       </c>
       <c r="U13" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="V13" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="W13" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X13" t="n">
         <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z13" t="n">
-        <v>6.25</v>
+        <v>5.25</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="AB13" t="n">
-        <v>3.04</v>
+        <v>2.75</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.77</v>
+        <v>2.15</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.93</v>
+        <v>1.67</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46030.5625</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.54</v>
+        <v>4.15</v>
       </c>
       <c r="M15" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="N15" t="n">
-        <v>4.55</v>
+        <v>1.8</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.44</v>
+        <v>2.03</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.62</v>
+        <v>1.88</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46030.60416666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.95</v>
+        <v>1.4</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.85</v>
+        <v>2.75</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2382,16 +2382,16 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46030.60416666666</v>
@@ -2444,37 +2444,37 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.21</v>
+        <v>2.45</v>
       </c>
       <c r="M17" t="n">
-        <v>3.17</v>
+        <v>2.9</v>
       </c>
       <c r="N17" t="n">
-        <v>3.31</v>
+        <v>3.2</v>
       </c>
       <c r="O17" t="n">
         <v>3.22</v>
       </c>
       <c r="P17" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="R17" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="S17" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="T17" t="n">
-        <v>3.48</v>
+        <v>3.55</v>
       </c>
       <c r="U17" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="V17" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W17" t="n">
         <v>1.02</v>
@@ -2483,31 +2483,31 @@
         <v>1.06</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.69</v>
+        <v>2.63</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.17</v>
+        <v>2.55</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.7</v>
+        <v>1.51</v>
       </c>
       <c r="AC17" t="n">
-        <v>4.55</v>
+        <v>4.65</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AH17" t="n">
         <v>1.56</v>
@@ -2682,61 +2682,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="M19" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="N19" t="n">
-        <v>7.6</v>
+        <v>8.5</v>
       </c>
       <c r="O19" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="P19" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="Q19" t="n">
-        <v>7</v>
+        <v>6.75</v>
       </c>
       <c r="R19" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="S19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T19" t="n">
         <v>2.85</v>
       </c>
-      <c r="T19" t="n">
-        <v>3.17</v>
-      </c>
       <c r="U19" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V19" t="n">
         <v>8</v>
       </c>
       <c r="W19" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X19" t="n">
         <v>1.07</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.17</v>
+        <v>3.01</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.98</v>
+        <v>2.22</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.6</v>
+        <v>3.68</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE19" t="n">
         <v>2.29</v>
@@ -2745,10 +2745,10 @@
         <v>1.56</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.84</v>
+        <v>2.74</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46030.69791666666</v>

--- a/jogos_2026-01-08.xlsx
+++ b/jogos_2026-01-08.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,25 +990,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.11</v>
+        <v>1.85</v>
       </c>
       <c r="M5" t="n">
-        <v>3.05</v>
+        <v>2.82</v>
       </c>
       <c r="N5" t="n">
-        <v>3.61</v>
+        <v>4.58</v>
       </c>
       <c r="O5" t="n">
-        <v>2.93</v>
+        <v>2.66</v>
       </c>
       <c r="P5" t="n">
-        <v>1.84</v>
+        <v>1.76</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.3</v>
+        <v>6</v>
       </c>
       <c r="R5" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="S5" t="n">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="T5" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="U5" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="V5" t="n">
         <v>11</v>
       </c>
       <c r="W5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.23</v>
+        <v>2.02</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.74</v>
+        <v>3.02</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="AC5" t="n">
-        <v>5.8</v>
+        <v>6.25</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.28</v>
+        <v>2.56</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.55</v>
+        <v>1.43</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.59</v>
+        <v>1.73</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46030.41666666666</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,25 +1109,25 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.85</v>
+        <v>2.11</v>
       </c>
       <c r="M6" t="n">
-        <v>2.82</v>
+        <v>3.05</v>
       </c>
       <c r="N6" t="n">
-        <v>4.58</v>
+        <v>3.61</v>
       </c>
       <c r="O6" t="n">
-        <v>2.66</v>
+        <v>2.93</v>
       </c>
       <c r="P6" t="n">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="Q6" t="n">
-        <v>6</v>
+        <v>4.3</v>
       </c>
       <c r="R6" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="S6" t="n">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="T6" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="U6" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="V6" t="n">
         <v>11</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X6" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.69</v>
+        <v>1.58</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.02</v>
+        <v>2.23</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.02</v>
+        <v>2.74</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>6.25</v>
+        <v>5.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.56</v>
+        <v>2.28</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.73</v>
+        <v>1.59</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46030.41666666666</v>
@@ -2070,20 +2070,20 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L14" t="n">
@@ -2189,20 +2189,20 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L15" t="n">
@@ -2308,10 +2308,10 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L16" t="n">
@@ -2427,20 +2427,20 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L17" t="n">
@@ -2546,10 +2546,10 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L18" t="n">
@@ -2665,20 +2665,20 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L19" t="n">
@@ -2797,23 +2797,23 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L20" t="n">
         <v>1.57</v>
       </c>
       <c r="M20" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="N20" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="O20" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="P20" t="n">
-        <v>2.19</v>
+        <v>2.26</v>
       </c>
       <c r="Q20" t="n">
         <v>5.2</v>
@@ -2822,10 +2822,10 @@
         <v>1.33</v>
       </c>
       <c r="S20" t="n">
-        <v>3.02</v>
+        <v>3.08</v>
       </c>
       <c r="T20" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="U20" t="n">
         <v>1.44</v>
@@ -2834,7 +2834,7 @@
         <v>6.5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X20" t="n">
         <v>1.03</v>
@@ -2843,31 +2843,31 @@
         <v>1.23</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.5</v>
+        <v>3.68</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.19</v>
+        <v>3.11</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AG20" t="n">
         <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46030.70833333334</v>

--- a/jogos_2026-01-08.xlsx
+++ b/jogos_2026-01-08.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,22 +871,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.66</v>
+        <v>2.25</v>
       </c>
       <c r="M4" t="n">
-        <v>3.87</v>
+        <v>3.2</v>
       </c>
       <c r="N4" t="n">
-        <v>4.4</v>
+        <v>2.79</v>
       </c>
       <c r="O4" t="n">
-        <v>2.16</v>
+        <v>3.14</v>
       </c>
       <c r="P4" t="n">
-        <v>2.19</v>
+        <v>1.77</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.05</v>
+        <v>4.5</v>
       </c>
       <c r="R4" t="n">
-        <v>1.33</v>
+        <v>1.65</v>
       </c>
       <c r="S4" t="n">
-        <v>3.02</v>
+        <v>2.2</v>
       </c>
       <c r="T4" t="n">
-        <v>2.53</v>
+        <v>3.75</v>
       </c>
       <c r="U4" t="n">
-        <v>1.48</v>
+        <v>1.17</v>
       </c>
       <c r="V4" t="n">
-        <v>6.25</v>
+        <v>9.4</v>
       </c>
       <c r="W4" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.18</v>
+        <v>1.61</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.6</v>
+        <v>2.12</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.72</v>
+        <v>3.05</v>
       </c>
       <c r="AB4" t="n">
-        <v>2</v>
+        <v>1.38</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.74</v>
+        <v>6.1</v>
       </c>
       <c r="AD4" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AG4" t="n">
         <v>1.35</v>
       </c>
-      <c r="AE4" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH4" t="n">
-        <v>2.1</v>
+        <v>1.49</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46030.41666666666</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,25 +1109,25 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.11</v>
+        <v>3</v>
       </c>
       <c r="M6" t="n">
-        <v>3.05</v>
+        <v>2.45</v>
       </c>
       <c r="N6" t="n">
-        <v>3.61</v>
+        <v>2.5</v>
       </c>
       <c r="O6" t="n">
-        <v>2.93</v>
+        <v>3.8</v>
       </c>
       <c r="P6" t="n">
-        <v>1.84</v>
+        <v>1.69</v>
       </c>
       <c r="Q6" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="T6" t="n">
         <v>4.3</v>
       </c>
-      <c r="R6" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="T6" t="n">
-        <v>3.6</v>
-      </c>
       <c r="U6" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="V6" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="W6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.23</v>
+        <v>2.01</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.74</v>
+        <v>3.08</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AC6" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.28</v>
+        <v>2.41</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="AG6" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AH6" t="n">
         <v>1.32</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.59</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46030.41666666666</v>
@@ -1228,25 +1228,25 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" t="n">
         <v>1</v>
       </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="M7" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="N7" t="n">
-        <v>2.79</v>
+        <v>3.61</v>
       </c>
       <c r="O7" t="n">
-        <v>3.14</v>
+        <v>2.93</v>
       </c>
       <c r="P7" t="n">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="R7" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="S7" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="T7" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="U7" t="n">
         <v>1.17</v>
       </c>
       <c r="V7" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="W7" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X7" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.05</v>
+        <v>2.74</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AC7" t="n">
-        <v>6.1</v>
+        <v>5.8</v>
       </c>
       <c r="AD7" t="n">
         <v>1.07</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.49</v>
+        <v>1.59</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46030.41666666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,99 +1347,99 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="N8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V8" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X8" t="n">
         <v>1</v>
       </c>
-      <c r="H8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L8" t="n">
-        <v>3</v>
-      </c>
-      <c r="M8" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="N8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O8" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="T8" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="V8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.12</v>
-      </c>
       <c r="Y8" t="n">
-        <v>1.7</v>
+        <v>1.18</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.01</v>
+        <v>3.6</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.08</v>
+        <v>1.72</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.28</v>
+        <v>2</v>
       </c>
       <c r="AC8" t="n">
-        <v>6.6</v>
+        <v>2.74</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.05</v>
+        <v>1.35</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.41</v>
+        <v>1.72</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.46</v>
+        <v>1.98</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.32</v>
+        <v>2.1</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46030.41666666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,25 +2180,25 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>4.15</v>
+        <v>2.45</v>
       </c>
       <c r="M15" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O15" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T15" t="n">
         <v>3.55</v>
       </c>
-      <c r="N15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="O15" t="n">
-        <v>4.37</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.65</v>
-      </c>
       <c r="U15" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="V15" t="n">
-        <v>6.75</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.32</v>
+        <v>1.47</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.08</v>
+        <v>2.63</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.03</v>
+        <v>2.55</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.88</v>
+        <v>1.51</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.65</v>
+        <v>4.65</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.22</v>
+        <v>1.41</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.13</v>
+        <v>1.56</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46030.60416666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,25 +2418,25 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.45</v>
+        <v>4.15</v>
       </c>
       <c r="M17" t="n">
-        <v>2.9</v>
+        <v>3.55</v>
       </c>
       <c r="N17" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="O17" t="n">
-        <v>3.22</v>
+        <v>4.37</v>
       </c>
       <c r="P17" t="n">
-        <v>1.9</v>
+        <v>2.07</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.1</v>
+        <v>2.3</v>
       </c>
       <c r="R17" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="S17" t="n">
-        <v>2.38</v>
+        <v>2.62</v>
       </c>
       <c r="T17" t="n">
-        <v>3.55</v>
+        <v>2.65</v>
       </c>
       <c r="U17" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="V17" t="n">
-        <v>9.199999999999999</v>
+        <v>6.75</v>
       </c>
       <c r="W17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X17" t="n">
         <v>1.02</v>
       </c>
-      <c r="X17" t="n">
-        <v>1.06</v>
-      </c>
       <c r="Y17" t="n">
-        <v>1.47</v>
+        <v>1.32</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.63</v>
+        <v>3.08</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.55</v>
+        <v>2.03</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.51</v>
+        <v>1.88</v>
       </c>
       <c r="AC17" t="n">
-        <v>4.65</v>
+        <v>3.65</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AE17" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.41</v>
+        <v>1.22</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.56</v>
+        <v>1.13</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46030.60416666666</v>
@@ -2903,54 +2903,54 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.85</v>
+        <v>2.04</v>
       </c>
       <c r="M21" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="N21" t="n">
         <v>3.6</v>
       </c>
       <c r="O21" t="n">
-        <v>2.61</v>
+        <v>2.56</v>
       </c>
       <c r="P21" t="n">
         <v>2</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.57</v>
+        <v>4.68</v>
       </c>
       <c r="R21" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S21" t="n">
-        <v>2.47</v>
+        <v>2.67</v>
       </c>
       <c r="T21" t="n">
-        <v>3</v>
+        <v>3.37</v>
       </c>
       <c r="U21" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="V21" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="W21" t="n">
         <v>1.02</v>
@@ -2959,19 +2959,19 @@
         <v>1.03</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.05</v>
+        <v>2.78</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.85</v>
+        <v>2.19</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.85</v>
+        <v>1.64</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.55</v>
+        <v>3.82</v>
       </c>
       <c r="AD21" t="n">
         <v>1.18</v>
@@ -2983,10 +2983,10 @@
         <v>1.8</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46030.71875</v>
